--- a/tame_output/ON/bt/strategyON_20240620.xlsx
+++ b/tame_output/ON/bt/strategyON_20240620.xlsx
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>55.9%</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.1%</t>
+          <t>109.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.6%</t>
+          <t>123.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.9%</t>
+          <t>-70.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.8%</t>
+          <t>455.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-11.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-567.0%</t>
+          <t>-565.6%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-47.1%</t>
+          <t>-47.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-196.4%</t>
+          <t>-195.8%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-22.0%</t>
+          <t>-21.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-14.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-191.3%</t>
+          <t>-219.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-218.1%</t>
+          <t>-217.6%</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-100.4%</t>
+          <t>-100.2%</t>
         </is>
       </c>
     </row>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.5027903991417</v>
+        <v>3.502790399141699</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.48587859441027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940719</v>
+        <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67684154977058</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.768951674611567</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.78056104342617</v>
+        <v>-4.708054543448152</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7842160671169893</v>
+        <v>0.8132186671081965</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2896107876403166</v>
+        <v>-0.2560055452085914</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.523030436217015</v>
+        <v>2.54319358167605</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.748085457255398</v>
+        <v>-4.67557895727738</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7948062631396149</v>
+        <v>0.823808863130822</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2896107876403166</v>
+        <v>-0.2560055452085914</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.520630397771332</v>
+        <v>2.540793543230367</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.7290473295481</v>
+        <v>-4.656540829570083</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7989462334307786</v>
+        <v>0.8279488334219858</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3477943989715111</v>
+        <v>-0.3141891565397859</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.48224495018086</v>
+        <v>2.502408095639895</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.760173960698719</v>
+        <v>-4.687667460720701</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.964077449909212</v>
+        <v>0.9930800499004191</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3477943989715111</v>
+        <v>-0.3141891565397859</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.65982681911954</v>
+        <v>2.679989964578576</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.774040722032637</v>
+        <v>-4.701534222054619</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9593640743617784</v>
+        <v>0.9883666743529855</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.385652315705334</v>
+        <v>-0.3520470732736088</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.63794539806538</v>
+        <v>2.658108543524415</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.794298020561595</v>
+        <v>-4.721791520583577</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.957269685347121</v>
+        <v>0.9862722853383281</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.385652315705334</v>
+        <v>-0.3520470732736088</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.643953928462306</v>
+        <v>2.664117073921341</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.646555050326592</v>
+        <v>-4.574048550348574</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.095519521233144</v>
+        <v>1.124522121224351</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2178449584704509</v>
+        <v>-0.1842397160387257</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.823790990595258</v>
+        <v>2.843954136054293</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.748569732857813</v>
+        <v>-4.676063232879796</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.057507269752136</v>
+        <v>1.086509869743344</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2178449584704509</v>
+        <v>-0.1842397160387257</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.826584612126739</v>
+        <v>2.846747757585774</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.742417026805029</v>
+        <v>-4.669910526827011</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.060630700564908</v>
+        <v>1.089633300556116</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.2116922524176666</v>
+        <v>-0.1780870099859414</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.830938584150068</v>
+        <v>2.851101729609103</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.759226324955531</v>
+        <v>-4.686719824977513</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.052987458044818</v>
+        <v>1.081990058036025</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.2285015505681682</v>
+        <v>-0.194896308136443</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.819933481999877</v>
+        <v>2.840096627458912</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.696928326179409</v>
+        <v>-4.624421826201391</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.144242211352088</v>
+        <v>1.173244811343295</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.2285015505681682</v>
+        <v>-0.194896308136443</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.886269035796698</v>
+        <v>2.906432181255733</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.495138128514251</v>
+        <v>-4.422631628536233</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9335391628075491</v>
+        <v>0.9625417627987563</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.03048335839901384</v>
+        <v>0.003121884032711353</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.713660823487589</v>
+        <v>2.733823968946623</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.435247446871657</v>
+        <v>-4.36274094689364</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.027785667786762</v>
+        <v>1.056788267777969</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.02940732324357964</v>
+        <v>0.06301256567530483</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.81988546479532</v>
+        <v>2.840048610254355</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.532987991496632</v>
+        <v>-4.460481491518614</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.003317186052815</v>
+        <v>1.032319786044023</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.01351804511059945</v>
+        <v>0.04712328754232464</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.824979634031576</v>
+        <v>2.84514277949061</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.709325751619561</v>
+        <v>-4.636819251641543</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9313180628283155</v>
+        <v>0.9603206628195227</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.1628197150123299</v>
+        <v>-0.1292144725806048</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.71771295878249</v>
+        <v>2.737876104241525</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.637779428842684</v>
+        <v>-4.565272928864666</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9584282099789947</v>
+        <v>0.9874308099702018</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.1628197150123299</v>
+        <v>-0.1292144725806048</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.716204576822418</v>
+        <v>2.736367722281453</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.593406297204115</v>
+        <v>-4.520899797226098</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9760403300698584</v>
+        <v>1.005042930061065</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.1184465833737613</v>
+        <v>-0.08484134094203616</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.742691323240996</v>
+        <v>2.76285446870003</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.585452326909343</v>
+        <v>-4.512945826931325</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9792219181877673</v>
+        <v>1.008224518178974</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.1184465833737613</v>
+        <v>-0.08484134094203616</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.742691323240996</v>
+        <v>2.76285446870003</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.537796596348287</v>
+        <v>-4.46529009637027</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.004665967439994</v>
+        <v>1.033668567431201</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.0707908528127057</v>
+        <v>-0.0371856103809805</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.777666518605433</v>
+        <v>2.797829664064468</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.410112286553991</v>
+        <v>-4.337605786575973</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.060632064732438</v>
+        <v>1.089634664723645</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.05689345698159076</v>
+        <v>0.09049869941331595</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.859169477856736</v>
+        <v>2.879332623315771</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.470778876956381</v>
+        <v>-4.398272376978362</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.023120101047354</v>
+        <v>1.052122701038562</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.02480485973694291</v>
+        <v>0.008800382694782283</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.796905160301488</v>
+        <v>2.817068305760523</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.425940475347982</v>
+        <v>-4.353433975369963</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.045153164301342</v>
+        <v>1.074155764292549</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.02026142679207343</v>
+        <v>0.01334381563965176</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.803728922679039</v>
+        <v>2.823892068138073</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.52669911110498</v>
+        <v>-4.454192611126961</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.009010649629621</v>
+        <v>1.038013249620828</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.1090869955190789</v>
+        <v>-0.07548175308735366</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.754594521073913</v>
+        <v>2.774757666532948</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.48249627401908</v>
+        <v>-4.409989774041061</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.032571386991818</v>
+        <v>1.061573986983026</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.06488415843317841</v>
+        <v>-0.03127891600145322</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.78699582585329</v>
+        <v>2.807158971312326</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.519475301682522</v>
+        <v>-4.446968801704504</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.016189776395689</v>
+        <v>1.045192376386896</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.02791025664184787</v>
+        <v>0.005694985789877316</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.807590167397336</v>
+        <v>2.827753312856371</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.539533380547363</v>
+        <v>-4.467026880569344</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.059414310032792</v>
+        <v>1.088416910024</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.02791025664184787</v>
+        <v>0.005694985789877316</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.858837932580376</v>
+        <v>2.879001078039411</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.499602707369473</v>
+        <v>-4.427096207391454</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.073827283898201</v>
+        <v>1.102829883889409</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.01202041653604247</v>
+        <v>0.04562565896776766</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.881237041081363</v>
+        <v>2.901400186540398</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.448570614646945</v>
+        <v>-4.376064114668926</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.089188349225482</v>
+        <v>1.11819094921669</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.06305250925857042</v>
+        <v>0.09665775169029561</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.90680452495315</v>
+        <v>2.926967670412185</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.38334643351974</v>
+        <v>-4.310839933541721</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.132465425769069</v>
+        <v>1.161468025760277</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.128276690385776</v>
+        <v>0.1618819328175012</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.963126437722178</v>
+        <v>2.983289583181214</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.345919413448605</v>
+        <v>-4.273412913470587</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.143397206096803</v>
+        <v>1.172399806088011</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.1335282284149577</v>
+        <v>0.1671334708466829</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.962238332838968</v>
+        <v>2.982401478298003</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.366031069483314</v>
+        <v>-4.293524569505295</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.13660933601416</v>
+        <v>1.165611936005368</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.1445555734123769</v>
+        <v>0.1781608158441021</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.97011153216866</v>
+        <v>2.990274677627695</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.312286255056109</v>
+        <v>-4.23977975507809</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.318665032806253</v>
+        <v>1.347667632797461</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.1546188828528389</v>
+        <v>0.1882241252845641</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.136707288854148</v>
+        <v>3.156870434313183</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.288494686449967</v>
+        <v>-4.215988186471948</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.448294569466527</v>
+        <v>1.477297169457735</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.1784104514589812</v>
+        <v>0.2120156938907063</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.27109513923565</v>
+        <v>3.291258284694685</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.325249105011689</v>
+        <v>-4.252742605033671</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.425300778055697</v>
+        <v>1.454303378046905</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.1784104514589812</v>
+        <v>0.2120156938907063</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.262803115249509</v>
+        <v>3.282966260708544</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.320914801954642</v>
+        <v>-4.248408301976623</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.425227694862296</v>
+        <v>1.454230294853503</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.3300605547781851</v>
+        <v>0.3636657972099103</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.351986372824811</v>
+        <v>3.372149518283846</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.312022340561358</v>
+        <v>-4.23951584058334</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.4463390851464</v>
+        <v>1.475341685137608</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.3300605547781851</v>
+        <v>0.3636657972099103</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.369540778551603</v>
+        <v>3.389703924010637</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.480498457531236</v>
+        <v>-4.407991957553217</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.370803685763033</v>
+        <v>1.399806285754241</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.3021127190616043</v>
+        <v>0.3357179614933295</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.344627124526238</v>
+        <v>3.364790269985273</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.233772154546119</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.782698928669653</v>
+        <v>-3.710192428691634</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.72033615876451</v>
+        <v>1.749338758755718</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.2317646596911936</v>
+        <v>0.2653699021229188</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.372830950360835</v>
+        <v>3.39299409581987</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.224436177043023</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.7599778249865</v>
+        <v>-3.687471325008481</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.720088622734676</v>
+        <v>1.749091222725883</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.2317646596911936</v>
+        <v>0.2653699021229188</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.363494972857739</v>
+        <v>3.383658118316775</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.383342302894192</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.900270424523693</v>
+        <v>-3.827763924545674</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.822877708770968</v>
+        <v>1.851880308762175</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.09147206015400094</v>
+        <v>0.1250773025857261</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.438225538986593</v>
+        <v>3.458388684445628</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.840448356612856</v>
+        <v>3.839440314291286</v>
       </c>
       <c r="C2000" t="n">
         <v>3.420420125387839</v>
       </c>
       <c r="D2000" t="n">
-        <v>-4.053887398711301</v>
+        <v>-4.040357069588407</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.798508741589571</v>
+        <v>1.803920873238729</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.05937567285221973</v>
+        <v>0.06367719980829367</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.456045529099171</v>
+        <v>3.458626445272815</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240620.xlsx
+++ b/tame_output/ON/bt/strategyON_20240620.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>62.0%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.4%</t>
+          <t>-74.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.2%</t>
+          <t>108.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.8%</t>
+          <t>123.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.8%</t>
+          <t>-69.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>455.0%</t>
+          <t>454.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.2%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-565.6%</t>
+          <t>-542.9%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-47.3%</t>
+          <t>-46.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-195.8%</t>
+          <t>-186.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-21.9%</t>
+          <t>-18.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-14.9%</t>
+          <t>-10.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-219.0%</t>
+          <t>-162.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-217.6%</t>
+          <t>-194.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-100.2%</t>
+          <t>-86.0%</t>
         </is>
       </c>
     </row>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141699</v>
+        <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440632</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587859441027</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390584</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.691571733940719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812101</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646215</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611567</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.708054543448152</v>
+        <v>-4.78056104342617</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8132186671081965</v>
+        <v>0.7842160671169893</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2560055452085914</v>
+        <v>-0.2896107876403166</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.54319358167605</v>
+        <v>2.523030436217015</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.67557895727738</v>
+        <v>-4.748085457255398</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.823808863130822</v>
+        <v>0.7948062631396149</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2560055452085914</v>
+        <v>-0.2896107876403166</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.540793543230367</v>
+        <v>2.520630397771332</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.656540829570083</v>
+        <v>-4.7290473295481</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8279488334219858</v>
+        <v>0.7989462334307786</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3141891565397859</v>
+        <v>-0.3477943989715111</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.502408095639895</v>
+        <v>2.48224495018086</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.687667460720701</v>
+        <v>-4.760173960698719</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9930800499004191</v>
+        <v>0.964077449909212</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3141891565397859</v>
+        <v>-0.3477943989715111</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.679989964578576</v>
+        <v>2.65982681911954</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.701534222054619</v>
+        <v>-4.774040722032637</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9883666743529855</v>
+        <v>0.9593640743617784</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.3520470732736088</v>
+        <v>-0.385652315705334</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.658108543524415</v>
+        <v>2.63794539806538</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.721791520583577</v>
+        <v>-4.794298020561595</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9862722853383281</v>
+        <v>0.957269685347121</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.3520470732736088</v>
+        <v>-0.385652315705334</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.664117073921341</v>
+        <v>2.643953928462306</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.574048550348574</v>
+        <v>-4.646555050326592</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.124522121224351</v>
+        <v>1.095519521233144</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.1842397160387257</v>
+        <v>-0.2178449584704509</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.843954136054293</v>
+        <v>2.823790990595258</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.676063232879796</v>
+        <v>-4.748569732857813</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.086509869743344</v>
+        <v>1.057507269752136</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.1842397160387257</v>
+        <v>-0.2178449584704509</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.846747757585774</v>
+        <v>2.826584612126739</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.669910526827011</v>
+        <v>-4.742417026805029</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.089633300556116</v>
+        <v>1.060630700564908</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.1780870099859414</v>
+        <v>-0.2116922524176666</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.851101729609103</v>
+        <v>2.830938584150068</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.686719824977513</v>
+        <v>-4.759226324955531</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.081990058036025</v>
+        <v>1.052987458044818</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.194896308136443</v>
+        <v>-0.2285015505681682</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.840096627458912</v>
+        <v>2.819933481999877</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.624421826201391</v>
+        <v>-4.696928326179409</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.173244811343295</v>
+        <v>1.144242211352088</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.194896308136443</v>
+        <v>-0.2285015505681682</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.906432181255733</v>
+        <v>2.886269035796698</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.422631628536233</v>
+        <v>-4.495138128514251</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9625417627987563</v>
+        <v>0.9335391628075491</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.003121884032711353</v>
+        <v>-0.03048335839901384</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.733823968946623</v>
+        <v>2.713660823487589</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.36274094689364</v>
+        <v>-4.435247446871657</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.056788267777969</v>
+        <v>1.027785667786762</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.06301256567530483</v>
+        <v>0.02940732324357964</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.840048610254355</v>
+        <v>2.81988546479532</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.460481491518614</v>
+        <v>-4.532987991496632</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.032319786044023</v>
+        <v>1.003317186052815</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.04712328754232464</v>
+        <v>0.01351804511059945</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.84514277949061</v>
+        <v>2.824979634031576</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.636819251641543</v>
+        <v>-4.4673154331483</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9603206628195227</v>
+        <v>1.02812219021682</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.1292144725806048</v>
+        <v>0.07919060345893031</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.737876104241525</v>
+        <v>2.862919149865246</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.565272928864666</v>
+        <v>-4.395769110371424</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9874308099702018</v>
+        <v>1.055232337367499</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.1292144725806048</v>
+        <v>0.07919060345893031</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.736367722281453</v>
+        <v>2.861410767905174</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.520899797226098</v>
+        <v>-4.351395978732855</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.005042930061065</v>
+        <v>1.072844457458363</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.08484134094203616</v>
+        <v>0.1235637350974989</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.76285446870003</v>
+        <v>2.887897514323751</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.512945826931325</v>
+        <v>-4.343442008438083</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.008224518178974</v>
+        <v>1.076026045576272</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.08484134094203616</v>
+        <v>0.1235637350974989</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.76285446870003</v>
+        <v>2.887897514323751</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.46529009637027</v>
+        <v>-4.295786277877027</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.033668567431201</v>
+        <v>1.101470094828499</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.0371856103809805</v>
+        <v>0.1712194656585546</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.797829664064468</v>
+        <v>2.922872709688189</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.337605786575973</v>
+        <v>-4.16810196808273</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.089634664723645</v>
+        <v>1.157436192120942</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.09049869941331595</v>
+        <v>0.298903775452851</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.879332623315771</v>
+        <v>3.004375668939492</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.398272376978362</v>
+        <v>-4.22876855848512</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.052122701038562</v>
+        <v>1.119924228435858</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.008800382694782283</v>
+        <v>0.2172054587343173</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.817068305760523</v>
+        <v>2.942111351384244</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.353433975369963</v>
+        <v>-4.183930156876722</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.074155764292549</v>
+        <v>1.141957291689846</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.01334381563965176</v>
+        <v>0.2217488916791868</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.823892068138073</v>
+        <v>2.948935113761794</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.454192611126961</v>
+        <v>-4.28468879263372</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.038013249620828</v>
+        <v>1.105814777018125</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.07548175308735366</v>
+        <v>0.1329233229521814</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.774757666532948</v>
+        <v>2.899800712156669</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.409989774041061</v>
+        <v>-4.240485955547819</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.061573986983026</v>
+        <v>1.129375514380322</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.03127891600145322</v>
+        <v>0.1771261600380818</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.807158971312326</v>
+        <v>2.932202016936047</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.446968801704504</v>
+        <v>-4.277464983211262</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.045192376386896</v>
+        <v>1.112993903784193</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.005694985789877316</v>
+        <v>0.2141000618294124</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.827753312856371</v>
+        <v>2.952796358480092</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.467026880569344</v>
+        <v>-4.297523062076102</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.088416910024</v>
+        <v>1.156218437421296</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.005694985789877316</v>
+        <v>0.2141000618294124</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.879001078039411</v>
+        <v>3.004044123663132</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.427096207391454</v>
+        <v>-4.257592388898212</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.102829883889409</v>
+        <v>1.170631411286706</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.04562565896776766</v>
+        <v>0.2540307350073027</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.901400186540398</v>
+        <v>3.026443232164119</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.376064114668926</v>
+        <v>-4.206560296175684</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.11819094921669</v>
+        <v>1.185992476613987</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.09665775169029561</v>
+        <v>0.3050628277298307</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.926967670412185</v>
+        <v>3.052010716035906</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.310839933541721</v>
+        <v>-4.141336115048479</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.161468025760277</v>
+        <v>1.229269553157574</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.1618819328175012</v>
+        <v>0.3702870088570363</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.983289583181214</v>
+        <v>3.108332628804935</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.273412913470587</v>
+        <v>-4.103909094977345</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.172399806088011</v>
+        <v>1.240201333485308</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.1671334708466829</v>
+        <v>0.375538546886218</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.982401478298003</v>
+        <v>3.107444523921724</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.293524569505295</v>
+        <v>-4.124020751012053</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.165611936005368</v>
+        <v>1.233413463402665</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.1781608158441021</v>
+        <v>0.3865658918836372</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.990274677627695</v>
+        <v>3.115317723251416</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.23977975507809</v>
+        <v>-4.070275936584848</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.347667632797461</v>
+        <v>1.415469160194757</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.1882241252845641</v>
+        <v>0.3966292013240991</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.156870434313183</v>
+        <v>3.281913479936904</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.215988186471948</v>
+        <v>-4.046484367978707</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.477297169457735</v>
+        <v>1.545098696855031</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.2120156938907063</v>
+        <v>0.4204207699302414</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.291258284694685</v>
+        <v>3.416301330318406</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.252742605033671</v>
+        <v>-4.083238786540429</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.454303378046905</v>
+        <v>1.522104905444201</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.2120156938907063</v>
+        <v>0.4204207699302414</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.282966260708544</v>
+        <v>3.408009306332265</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.248408301976623</v>
+        <v>-4.078904483483381</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.454230294853503</v>
+        <v>1.5220318222508</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.3636657972099103</v>
+        <v>0.5720708732494453</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.372149518283846</v>
+        <v>3.497192563907567</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.23951584058334</v>
+        <v>-4.070012022090098</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.475341685137608</v>
+        <v>1.543143212534904</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.3636657972099103</v>
+        <v>0.5720708732494453</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.389703924010637</v>
+        <v>3.514746969634358</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.407991957553217</v>
+        <v>-4.238488139059975</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.399806285754241</v>
+        <v>1.467607813151538</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.3357179614933295</v>
+        <v>0.5441230375328645</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.364790269985273</v>
+        <v>3.489833315608994</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.233772154546119</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.710192428691634</v>
+        <v>-3.540688610198392</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.749338758755718</v>
+        <v>1.817140286153015</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.2653699021229188</v>
+        <v>0.4737749781624538</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.39299409581987</v>
+        <v>3.518037141443591</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.224436177043023</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.687471325008481</v>
+        <v>-3.51796750651524</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.749091222725883</v>
+        <v>1.81689275012318</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.2653699021229188</v>
+        <v>0.4737749781624538</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.383658118316775</v>
+        <v>3.508701163940496</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.383342302894192</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.827763924545674</v>
+        <v>-3.658260106052432</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.851880308762175</v>
+        <v>1.919681836159472</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.1250773025857261</v>
+        <v>0.3334823786252611</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.458388684445628</v>
+        <v>3.583431730069349</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.839440314291286</v>
+        <v>3.900481382115885</v>
       </c>
       <c r="C2000" t="n">
         <v>3.420420125387839</v>
       </c>
       <c r="D2000" t="n">
-        <v>-4.040357069588407</v>
+        <v>-3.813041112830687</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.803920873238729</v>
+        <v>1.894847255941817</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.06367719980829367</v>
+        <v>0.300114704570785</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.458626445272815</v>
+        <v>3.60048894813031</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240620.xlsx
+++ b/tame_output/ON/bt/strategyON_20240620.xlsx
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.5027903991417</v>
+        <v>3.502790399141699</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.48587859441027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940719</v>
+        <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67684154977058</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.768951674611567</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>

--- a/tame_output/ON/bt/strategyON_20240620.xlsx
+++ b/tame_output/ON/bt/strategyON_20240620.xlsx
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>74.2%</t>
+          <t>80.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,22 +849,22 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>52.2%</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.9%</t>
+          <t>109.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.2%</t>
+          <t>123.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-69.4%</t>
+          <t>-69.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.9%</t>
+          <t>455.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-542.9%</t>
+          <t>-541.6%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-46.7%</t>
+          <t>-46.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-186.7%</t>
+          <t>-186.2%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-18.3%</t>
+          <t>-18.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-162.4%</t>
+          <t>-166.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-194.0%</t>
+          <t>-193.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-17.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-86.0%</t>
+          <t>-82.9%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2000"/>
+  <dimension ref="A1:G2001"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341313</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626476</v>
+        <v>3.856161751626477</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539952</v>
+        <v>3.843274527539953</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.78056104342617</v>
+        <v>-4.708054543448152</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7842160671169893</v>
+        <v>0.8132186671081965</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2896107876403166</v>
+        <v>-0.2560055452085914</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.523030436217015</v>
+        <v>2.54319358167605</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.748085457255398</v>
+        <v>-4.67557895727738</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7948062631396149</v>
+        <v>0.823808863130822</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2896107876403166</v>
+        <v>-0.2560055452085914</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.520630397771332</v>
+        <v>2.540793543230367</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.7290473295481</v>
+        <v>-4.656540829570083</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7989462334307786</v>
+        <v>0.8279488334219858</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3477943989715111</v>
+        <v>-0.3141891565397859</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.48224495018086</v>
+        <v>2.502408095639895</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.760173960698719</v>
+        <v>-4.687667460720701</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.964077449909212</v>
+        <v>0.9930800499004191</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3477943989715111</v>
+        <v>-0.3141891565397859</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.65982681911954</v>
+        <v>2.679989964578576</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.774040722032637</v>
+        <v>-4.701534222054619</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9593640743617784</v>
+        <v>0.9883666743529855</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.385652315705334</v>
+        <v>-0.3520470732736088</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.63794539806538</v>
+        <v>2.658108543524415</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.794298020561595</v>
+        <v>-4.721791520583577</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.957269685347121</v>
+        <v>0.9862722853383281</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.385652315705334</v>
+        <v>-0.3520470732736088</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.643953928462306</v>
+        <v>2.664117073921341</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.646555050326592</v>
+        <v>-4.574048550348574</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.095519521233144</v>
+        <v>1.124522121224351</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2178449584704509</v>
+        <v>-0.1842397160387257</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.823790990595258</v>
+        <v>2.843954136054293</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.748569732857813</v>
+        <v>-4.676063232879796</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.057507269752136</v>
+        <v>1.086509869743344</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2178449584704509</v>
+        <v>-0.1842397160387257</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.826584612126739</v>
+        <v>2.846747757585774</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.742417026805029</v>
+        <v>-4.669910526827011</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.060630700564908</v>
+        <v>1.089633300556116</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.2116922524176666</v>
+        <v>-0.1780870099859414</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.830938584150068</v>
+        <v>2.851101729609103</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.759226324955531</v>
+        <v>-4.686719824977513</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.052987458044818</v>
+        <v>1.081990058036025</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.2285015505681682</v>
+        <v>-0.194896308136443</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.819933481999877</v>
+        <v>2.840096627458912</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.696928326179409</v>
+        <v>-4.624421826201391</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.144242211352088</v>
+        <v>1.173244811343295</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.2285015505681682</v>
+        <v>-0.194896308136443</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.886269035796698</v>
+        <v>2.906432181255733</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.495138128514251</v>
+        <v>-4.422631628536233</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9335391628075491</v>
+        <v>0.9625417627987563</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.03048335839901384</v>
+        <v>0.003121884032711353</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.713660823487589</v>
+        <v>2.733823968946623</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.435247446871657</v>
+        <v>-4.36274094689364</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.027785667786762</v>
+        <v>1.056788267777969</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.02940732324357964</v>
+        <v>0.06301256567530483</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.81988546479532</v>
+        <v>2.840048610254355</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.532987991496632</v>
+        <v>-4.460481491518614</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.003317186052815</v>
+        <v>1.032319786044023</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.01351804511059945</v>
+        <v>0.04712328754232464</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.824979634031576</v>
+        <v>2.84514277949061</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.4673154331483</v>
+        <v>-4.396802406287816</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.02812219021682</v>
+        <v>1.056327400961014</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.07919060345893031</v>
+        <v>0.1108023727731228</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.862919149865246</v>
+        <v>2.881886211453761</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.395769110371424</v>
+        <v>-4.325256083510939</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.055232337367499</v>
+        <v>1.083437548111693</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.07919060345893031</v>
+        <v>0.1108023727731228</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.861410767905174</v>
+        <v>2.880377829493689</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.351395978732855</v>
+        <v>-4.28088295187237</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.072844457458363</v>
+        <v>1.101049668202557</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.1235637350974989</v>
+        <v>0.1551755044116914</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.887897514323751</v>
+        <v>2.906864575912267</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.343442008438083</v>
+        <v>-4.272928981577598</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.076026045576272</v>
+        <v>1.104231256320465</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.1235637350974989</v>
+        <v>0.1551755044116914</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.887897514323751</v>
+        <v>2.906864575912267</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.295786277877027</v>
+        <v>-4.225273251016542</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.101470094828499</v>
+        <v>1.129675305572692</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.1712194656585546</v>
+        <v>0.202831234972747</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.922872709688189</v>
+        <v>2.941839771276705</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.16810196808273</v>
+        <v>-4.097588941222246</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.157436192120942</v>
+        <v>1.185641402865136</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.298903775452851</v>
+        <v>0.3305155447670435</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.004375668939492</v>
+        <v>3.023342730528008</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.22876855848512</v>
+        <v>-4.158255531624635</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.119924228435858</v>
+        <v>1.148129439180053</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.2172054587343173</v>
+        <v>0.2488172280485098</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.942111351384244</v>
+        <v>2.96107841297276</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.183930156876722</v>
+        <v>-4.113417130016236</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.141957291689846</v>
+        <v>1.170162502434041</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.2217488916791868</v>
+        <v>0.2533606609933793</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.948935113761794</v>
+        <v>2.96790217535031</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.28468879263372</v>
+        <v>-4.214175765773234</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.105814777018125</v>
+        <v>1.134019987762319</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.1329233229521814</v>
+        <v>0.1645350922663739</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.899800712156669</v>
+        <v>2.918767773745185</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.240485955547819</v>
+        <v>-4.169972928687334</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.129375514380322</v>
+        <v>1.157580725124516</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.1771261600380818</v>
+        <v>0.2087379293522743</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.932202016936047</v>
+        <v>2.951169078524562</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.277464983211262</v>
+        <v>-4.206951956350776</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.112993903784193</v>
+        <v>1.141199114528387</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.2141000618294124</v>
+        <v>0.2457118311436048</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.952796358480092</v>
+        <v>2.971763420068608</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.297523062076102</v>
+        <v>-4.227010035215617</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.156218437421296</v>
+        <v>1.18442364816549</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.2141000618294124</v>
+        <v>0.2457118311436048</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.004044123663132</v>
+        <v>3.023011185251648</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.257592388898212</v>
+        <v>-4.187079362037727</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.170631411286706</v>
+        <v>1.1988366220309</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.2540307350073027</v>
+        <v>0.2856425043214952</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.026443232164119</v>
+        <v>3.045410293752635</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.206560296175684</v>
+        <v>-4.136047269315199</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.185992476613987</v>
+        <v>1.214197687358181</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.3050628277298307</v>
+        <v>0.3366745970440231</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.052010716035906</v>
+        <v>3.070977777624422</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.141336115048479</v>
+        <v>-4.070823088187994</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.229269553157574</v>
+        <v>1.257474763901768</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.3702870088570363</v>
+        <v>0.4018987781712288</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.108332628804935</v>
+        <v>3.12729969039345</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.103909094977345</v>
+        <v>-4.033396068116859</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.240201333485308</v>
+        <v>1.268406544229502</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.375538546886218</v>
+        <v>0.4071503162004104</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.107444523921724</v>
+        <v>3.126411585510239</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.124020751012053</v>
+        <v>-4.053507724151568</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.233413463402665</v>
+        <v>1.261618674146859</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.3865658918836372</v>
+        <v>0.4181776611978296</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.115317723251416</v>
+        <v>3.134284784839931</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393551</v>
+        <v>3.828690479393552</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.070275936584848</v>
+        <v>-3.999762909724363</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.415469160194757</v>
+        <v>1.443674370938951</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.3966292013240991</v>
+        <v>0.4282409706382916</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.281913479936904</v>
+        <v>3.300880541525419</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714888</v>
+        <v>3.813251854714889</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.046484367978707</v>
+        <v>-3.975971341118221</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.545098696855031</v>
+        <v>1.573303907599226</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.4204207699302414</v>
+        <v>0.4520325392444339</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.416301330318406</v>
+        <v>3.435268391906922</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.083238786540429</v>
+        <v>-4.012725759679943</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.522104905444201</v>
+        <v>1.550310116188396</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.4204207699302414</v>
+        <v>0.4520325392444339</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.408009306332265</v>
+        <v>3.426976367920781</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.078904483483381</v>
+        <v>-4.008391456622894</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.5220318222508</v>
+        <v>1.550237032994995</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.5720708732494453</v>
+        <v>0.6036826425636378</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.497192563907567</v>
+        <v>3.516159625496083</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.070012022090098</v>
+        <v>-3.99949899522961</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.543143212534904</v>
+        <v>1.5713484232791</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.5720708732494453</v>
+        <v>0.6036826425636378</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.514746969634358</v>
+        <v>3.533714031222874</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.238488139059975</v>
+        <v>-4.167975112199487</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.467607813151538</v>
+        <v>1.495813023895733</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.5441230375328645</v>
+        <v>0.575734806847057</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.489833315608994</v>
+        <v>3.50880037719751</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.233772154546119</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.540688610198392</v>
+        <v>-3.470175583337904</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.817140286153015</v>
+        <v>1.845345496897209</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.4737749781624538</v>
+        <v>0.5053867474766462</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.518037141443591</v>
+        <v>3.537004203032107</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.224436177043023</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.51796750651524</v>
+        <v>-3.447454479654751</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.81689275012318</v>
+        <v>1.845097960867375</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.4737749781624538</v>
+        <v>0.5053867474766462</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.508701163940496</v>
+        <v>3.527668225529011</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.383342302894192</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.658260106052432</v>
+        <v>-3.587747079191944</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.919681836159472</v>
+        <v>1.947887046903667</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.3334823786252611</v>
+        <v>0.3650941479394536</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.583431730069349</v>
+        <v>3.602398791657865</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,45 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.900481382115885</v>
+        <v>3.779962759401677</v>
       </c>
       <c r="C2000" t="n">
         <v>3.420420125387839</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.813041112830687</v>
+        <v>-3.799872414931138</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.894847255941817</v>
+        <v>1.900114735101636</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.300114704570785</v>
+        <v>0.3037382022901745</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.60048894813031</v>
+        <v>3.602663046761944</v>
+      </c>
+    </row>
+    <row r="2001">
+      <c r="A2001" s="2" t="n">
+        <v>45463</v>
+      </c>
+      <c r="B2001" t="n">
+        <v>3.900877010053618</v>
+      </c>
+      <c r="C2001" t="n">
+        <v>3.637811418335678</v>
+      </c>
+      <c r="D2001" t="n">
+        <v>-3.799872414931138</v>
+      </c>
+      <c r="E2001" t="n">
+        <v>1.900114735101636</v>
+      </c>
+      <c r="F2001" t="n">
+        <v>0.3037382022901745</v>
+      </c>
+      <c r="G2001" t="n">
+        <v>3.630875215322046</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240620.xlsx
+++ b/tame_output/ON/bt/strategyON_20240620.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>29.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>80.5%</t>
+          <t>71.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>21.6%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.2%</t>
+          <t>-74.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.0%</t>
+          <t>108.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.3%</t>
+          <t>123.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.1%</t>
+          <t>93.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-69.5%</t>
+          <t>-70.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>455.1%</t>
+          <t>451.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-541.6%</t>
+          <t>-546.9%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>19.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-46.9%</t>
+          <t>-84.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-186.2%</t>
+          <t>-188.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-18.2%</t>
+          <t>-18.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-10.9%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-166.3%</t>
+          <t>-155.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-193.6%</t>
+          <t>-198.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-82.9%</t>
+          <t>-113.5%</t>
         </is>
       </c>
     </row>
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.291915294659031</v>
+        <v>-8.331682566110988</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.158371318015496</v>
+        <v>-0.1742782265962788</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.731025994628489</v>
+        <v>-1.770793266080445</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.120135627384771</v>
+        <v>2.096275264513597</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.142248903651517</v>
+        <v>-8.182016175103474</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1013969719254493</v>
+        <v>-0.1173038805062321</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.638122503385953</v>
+        <v>-1.677889774837909</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.172985511817333</v>
+        <v>2.14912514894616</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.009973430020629</v>
+        <v>-8.049740701472587</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.05311929572606733</v>
+        <v>-0.06902620430685014</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.505847029755066</v>
+        <v>-1.545614301207022</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.247718282742892</v>
+        <v>2.223857919871719</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.819373755347477</v>
+        <v>-7.859141026799434</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.02593563483083017</v>
+        <v>0.01002872625004736</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.315247355081913</v>
+        <v>-1.35501462653387</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.364893148234421</v>
+        <v>2.341032785363247</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.570373956663896</v>
+        <v>-7.610141228115853</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1384418955279214</v>
+        <v>0.1225349869471386</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.315247355081913</v>
+        <v>-1.35501462653387</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.377799489458079</v>
+        <v>2.353939126586906</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.675963946437</v>
+        <v>-7.715731217888957</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.03177002998053879</v>
+        <v>-0.04767693856132205</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.420837344855018</v>
+        <v>-1.460604616306974</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.186469565994998</v>
+        <v>2.162609203123824</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.694698848555597</v>
+        <v>-7.734466120007554</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.009280351049108404</v>
+        <v>-0.006626557531674404</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.426433354515149</v>
+        <v>-1.466200625967105</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.231656302076006</v>
+        <v>2.207795939204832</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.546758807147998</v>
+        <v>-7.586526078599955</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.05142255507601945</v>
+        <v>-0.06732946365680226</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.406112438606591</v>
+        <v>-1.445879710058548</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.123969928932973</v>
+        <v>2.100109566061799</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.493789284894009</v>
+        <v>-7.533556556345967</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.03894873242790187</v>
+        <v>-0.05485564100868512</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.353142916352602</v>
+        <v>-1.392910187804559</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.147037656031888</v>
+        <v>2.123177293160714</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.450240878123319</v>
+        <v>-7.490008149575276</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.02848998181471885</v>
+        <v>-0.0443968903955021</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.353142916352602</v>
+        <v>-1.392910187804559</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.140077043936795</v>
+        <v>2.116216681065621</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.208092484669461</v>
+        <v>-7.247859756121418</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.0828317299479675</v>
+        <v>0.06692482136718425</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.353142916352602</v>
+        <v>-1.392910187804559</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.154539398317938</v>
+        <v>2.130679035446764</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.099833347546939</v>
+        <v>-7.139600618998896</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1206675052561712</v>
+        <v>0.104760596675388</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.353142916352602</v>
+        <v>-1.392910187804559</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.149071518777133</v>
+        <v>2.125211155905959</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.976542212729808</v>
+        <v>-7.016309484181765</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1674820531936003</v>
+        <v>0.1515751446128175</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.229851781535472</v>
+        <v>-1.269619052987428</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.220544293677988</v>
+        <v>2.196683930806814</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.955393013826365</v>
+        <v>-6.995160285278322</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1836427109923027</v>
+        <v>0.1677358024115199</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.208702582632029</v>
+        <v>-1.248469854083985</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.240934791257379</v>
+        <v>2.217074428386205</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.711627571842921</v>
+        <v>-6.751394843294878</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2769295961327312</v>
+        <v>0.2610226875519484</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.208702582632029</v>
+        <v>-1.248469854083985</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.23671549960443</v>
+        <v>2.212855136733256</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.609864751565626</v>
+        <v>-6.649632023017583</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.319759038163665</v>
+        <v>0.3038521295828822</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.1954835142396</v>
+        <v>-1.235250785691556</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.246771254559903</v>
+        <v>2.222910891688729</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.360014357616551</v>
+        <v>-6.399781629068508</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4124412707269971</v>
+        <v>0.3965343621462143</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.1954835142396</v>
+        <v>-1.235250785691556</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.239513329543605</v>
+        <v>2.215652966672431</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.184122265149119</v>
+        <v>-6.223889536601076</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4863972312346188</v>
+        <v>0.4704903226538359</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.1954835142396</v>
+        <v>-1.235250785691556</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.243112453064254</v>
+        <v>2.21925209019308</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.012675802126656</v>
+        <v>-6.052443073578613</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5683033224981577</v>
+        <v>0.5523964139173749</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.024037051217137</v>
+        <v>-1.063804322669093</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.359307836932286</v>
+        <v>2.335447474061112</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.938386236388316</v>
+        <v>-5.978153507840274</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5970396264097904</v>
+        <v>0.5811327178290076</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.9497474854787973</v>
+        <v>-0.9895147569307536</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.402902053991586</v>
+        <v>2.379041691120412</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.874750494154382</v>
+        <v>-5.914517765606339</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6271887243576817</v>
+        <v>0.6112818157768984</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8861117432448627</v>
+        <v>-0.9258790146968191</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.445778300386264</v>
+        <v>2.421917937515091</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.763323734828462</v>
+        <v>-5.803091006280419</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6529536868718453</v>
+        <v>0.6370467782910625</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8861117432448627</v>
+        <v>-0.9258790146968191</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.42697255917006</v>
+        <v>2.403112196298886</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.522893238023602</v>
+        <v>-5.562660509475559</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7508689622186666</v>
+        <v>0.7349620536378838</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.6456812464400025</v>
+        <v>-0.6854485178919588</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.572973933877853</v>
+        <v>2.549113571006679</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.450650669852407</v>
+        <v>-5.490417941304364</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7836953033219647</v>
+        <v>0.7677883947411819</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.6456812464400025</v>
+        <v>-0.6854485178919588</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.576903247712674</v>
+        <v>2.5530428848415</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.397652347571019</v>
+        <v>-5.437419619022976</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8055732161518598</v>
+        <v>0.789666307571077</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5903449874380636</v>
+        <v>-0.63011225889002</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.610783587031177</v>
+        <v>2.586923224160003</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.288847462091292</v>
+        <v>-5.328614733543249</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8460932415637443</v>
+        <v>0.8301863329829615</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5903449874380636</v>
+        <v>-0.63011225889002</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.607781658251171</v>
+        <v>2.583921295379997</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.068826664054281</v>
+        <v>-5.108593935506239</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9356805977891627</v>
+        <v>0.9197736892083799</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4491251423700834</v>
+        <v>-0.4888924138220397</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.694092602302573</v>
+        <v>2.670232239431399</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.935958974991004</v>
+        <v>-4.975726246442961</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.004721856216297</v>
+        <v>0.9888149476355141</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4491251423700834</v>
+        <v>-0.4888924138220397</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.709986785104396</v>
+        <v>2.686126422233222</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.815785891626505</v>
+        <v>-4.855553163078462</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.053936934002398</v>
+        <v>1.038030025421615</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.3289520590055844</v>
+        <v>-0.3687193304575408</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.783236479563397</v>
+        <v>2.759376116692223</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.671113746526768</v>
+        <v>-4.710881017978725</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.121893894603733</v>
+        <v>1.10598698602295</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.184279913905847</v>
+        <v>-0.2240471853578034</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.88012786918468</v>
+        <v>2.856267506313506</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.73098857388446</v>
+        <v>-4.770755845336417</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.083981455062082</v>
+        <v>1.068074546481299</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2441547412635391</v>
+        <v>-0.2839220127154955</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.83024046417149</v>
+        <v>2.806380101300316</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.644189076105452</v>
+        <v>-4.683956347557409</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.141101747496251</v>
+        <v>1.125194838915469</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.2441547412635391</v>
+        <v>-0.2839220127154955</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.852640957494056</v>
+        <v>2.828780594622883</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.646658782567258</v>
+        <v>-4.686426054019215</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.140186266284941</v>
+        <v>1.124279357704158</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.2466244477253453</v>
+        <v>-0.2863917191773017</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.851231534990385</v>
+        <v>2.827371172119211</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.715028968891268</v>
+        <v>-4.754796240343225</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.123845114230039</v>
+        <v>1.107938205649256</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.2373487486891304</v>
+        <v>-0.2771160201410867</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.867803876886815</v>
+        <v>2.843943514015642</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.823567149807402</v>
+        <v>-4.863334421259359</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.070866550495477</v>
+        <v>1.054959641914694</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.2373487486891304</v>
+        <v>-0.2771160201410867</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.858240585518707</v>
+        <v>2.834380222647533</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.854560309136107</v>
+        <v>-4.894327580588064</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8831788518043815</v>
+        <v>0.8672719432235987</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.2373487486891304</v>
+        <v>-0.2771160201410867</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.682950150559094</v>
+        <v>2.65908978768792</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.679086049343638</v>
+        <v>-4.718853320795596</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9579357877131569</v>
+        <v>0.9420288791323739</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.2373487486891304</v>
+        <v>-0.2771160201410867</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.687517382550881</v>
+        <v>2.663657019679708</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.790022301984887</v>
+        <v>-4.829789573436845</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8893033154178642</v>
+        <v>0.8733964068370814</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.2373487486891304</v>
+        <v>-0.2771160201410867</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.663259411312088</v>
+        <v>2.639399048440915</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.756358756512605</v>
+        <v>-4.796126027964562</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9059001188266826</v>
+        <v>0.8899932102458998</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2036852032168485</v>
+        <v>-0.2434524746688049</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.686588923815363</v>
+        <v>2.662728560944189</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.696506137308882</v>
+        <v>-4.736273408760839</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9400135529403044</v>
+        <v>0.9241066443595214</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.2036852032168485</v>
+        <v>-0.2434524746688049</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.696761310247496</v>
+        <v>2.672900947376322</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.610262674282504</v>
+        <v>-4.650029945734461</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9694572087247157</v>
+        <v>0.9535503001439329</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.2036852032168485</v>
+        <v>-0.2434524746688049</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.691707580821356</v>
+        <v>2.667847217950182</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.655569493681484</v>
+        <v>-4.695336765133441</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9431102564096494</v>
+        <v>0.9272033478288666</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2444953662260793</v>
+        <v>-0.2842626376780357</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.658997258460343</v>
+        <v>2.635136895589169</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.684602598383785</v>
+        <v>-4.724369869835742</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9320488875618305</v>
+        <v>0.9161419789810477</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2444953662260793</v>
+        <v>-0.2842626376780357</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.659549131493445</v>
+        <v>2.635688768622271</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.591792116932925</v>
+        <v>-4.631559388384883</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8984457720335399</v>
+        <v>0.8825388634527571</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.15168488477522</v>
+        <v>-0.1914521562271763</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.644508112255326</v>
+        <v>2.620647749384152</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.636181586262353</v>
+        <v>-4.67594885771431</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8825634602263699</v>
+        <v>0.8666565516455869</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.1960743541046476</v>
+        <v>-0.235841625556604</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.61974790658227</v>
+        <v>2.595887543711096</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.523510368026103</v>
+        <v>-4.56327763947806</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9227076560325929</v>
+        <v>0.9068007474518101</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.08340313586839743</v>
+        <v>-0.1231704073203538</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.682426346035743</v>
+        <v>2.658565983164569</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.41113336684343</v>
+        <v>-4.450900638295387</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9731497523363293</v>
+        <v>0.9572428437555465</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.08340313586839743</v>
+        <v>-0.1231704073203538</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.68791764186641</v>
+        <v>2.664057278995236</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.438913764744782</v>
+        <v>-4.47868103619674</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9735347949443274</v>
+        <v>0.9576278863635443</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1111835337697505</v>
+        <v>-0.1509508052217068</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.682746604894138</v>
+        <v>2.658886242022964</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.521915045770061</v>
+        <v>-4.561682317222019</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7786900025348691</v>
+        <v>0.7627830939540861</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1297544182969242</v>
+        <v>-0.1695216897488806</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.509959794178487</v>
+        <v>2.486099431307313</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.630529124213393</v>
+        <v>-4.67029639566535</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8553940318767421</v>
+        <v>0.8394871232959593</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1297544182969242</v>
+        <v>-0.1695216897488806</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.630109454897692</v>
+        <v>2.606249092026518</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.717127707194495</v>
+        <v>-4.756894978646453</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.835267624786624</v>
+        <v>0.8193607162058412</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1297544182969242</v>
+        <v>-0.1695216897488806</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.644622481000015</v>
+        <v>2.620762118128841</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.678744044636344</v>
+        <v>-4.718511316088302</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8480405311522532</v>
+        <v>0.8321336225714702</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.09137075573877307</v>
+        <v>-0.1311380271907294</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.665072119877275</v>
+        <v>2.641211757006101</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.501627714601178</v>
+        <v>-4.541394986053136</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9156160920116214</v>
+        <v>0.8997091834308386</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.09137075573877307</v>
+        <v>-0.1311380271907294</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.661801148722577</v>
+        <v>2.637940785851403</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.546719959434724</v>
+        <v>-4.586487230886681</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8982625858401163</v>
+        <v>0.8823556772593335</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1532667989081629</v>
+        <v>-0.1930340703601192</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.625346914582856</v>
+        <v>2.601486551711682</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.367344538195956</v>
+        <v>-4.407111809647914</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9637997296420378</v>
+        <v>0.9478928210612549</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.003509959262555817</v>
+        <v>-0.03625731218940054</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.713199944791701</v>
+        <v>2.689339581920528</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.412358751716562</v>
+        <v>-4.452126023168519</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9266014995653853</v>
+        <v>0.9106945909846023</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.02683893605204879</v>
+        <v>-0.06660620750400514</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.675798062934528</v>
+        <v>2.651937700063355</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.679363261988997</v>
+        <v>-4.719130533440954</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.825491257795357</v>
+        <v>0.809584349214574</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2212019740949974</v>
+        <v>-0.2609692455469537</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.564871802447705</v>
+        <v>2.541011439576531</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.708054543448152</v>
+        <v>-4.820328314878127</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8132186671081965</v>
+        <v>0.7683091585362063</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2560055452085914</v>
+        <v>-0.3293780590922729</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.54319358167605</v>
+        <v>2.499170073345841</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.67557895727738</v>
+        <v>-4.787852728707355</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.823808863130822</v>
+        <v>0.7788993545588321</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2560055452085914</v>
+        <v>-0.3293780590922729</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.540793543230367</v>
+        <v>2.496770034900158</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.656540829570083</v>
+        <v>-4.768814601000058</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8279488334219858</v>
+        <v>0.7830393248499958</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3141891565397859</v>
+        <v>-0.3875616704234675</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.502408095639895</v>
+        <v>2.458384587309686</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.687667460720701</v>
+        <v>-4.799941232150676</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9930800499004191</v>
+        <v>0.9481705413284289</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3141891565397859</v>
+        <v>-0.3875616704234675</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.679989964578576</v>
+        <v>2.635966456248366</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.701534222054619</v>
+        <v>-4.813807993484594</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9883666743529855</v>
+        <v>0.9434571657809954</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.3520470732736088</v>
+        <v>-0.4254195871572904</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.658108543524415</v>
+        <v>2.614085035194206</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.721791520583577</v>
+        <v>-4.834065292013552</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9862722853383281</v>
+        <v>0.9413627767663382</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.3520470732736088</v>
+        <v>-0.4254195871572904</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.664117073921341</v>
+        <v>2.620093565591132</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.574048550348574</v>
+        <v>-4.686322321778549</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.124522121224351</v>
+        <v>1.079612612652361</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.1842397160387257</v>
+        <v>-0.2576122299224072</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.843954136054293</v>
+        <v>2.799930627724084</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.676063232879796</v>
+        <v>-4.788337004309771</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.086509869743344</v>
+        <v>1.041600361171354</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.1842397160387257</v>
+        <v>-0.2576122299224072</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.846747757585774</v>
+        <v>2.802724249255565</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.669910526827011</v>
+        <v>-4.782184298256986</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.089633300556116</v>
+        <v>1.044723791984126</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.1780870099859414</v>
+        <v>-0.2514595238696229</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.851101729609103</v>
+        <v>2.807078221278894</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.686719824977513</v>
+        <v>-4.798993596407488</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.081990058036025</v>
+        <v>1.037080549464035</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.194896308136443</v>
+        <v>-0.2682688220201246</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.840096627458912</v>
+        <v>2.796073119128703</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.624421826201391</v>
+        <v>-4.736695597631366</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.173244811343295</v>
+        <v>1.128335302771305</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.194896308136443</v>
+        <v>-0.2682688220201246</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.906432181255733</v>
+        <v>2.862408672925524</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.422631628536233</v>
+        <v>-4.534905399966208</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9625417627987563</v>
+        <v>0.9176322542267661</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.003121884032711353</v>
+        <v>-0.07025062985097019</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.733823968946623</v>
+        <v>2.689800460616415</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.36274094689364</v>
+        <v>-4.475014718323615</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.056788267777969</v>
+        <v>1.011878759205979</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.06301256567530483</v>
+        <v>-0.01035994820837671</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.840048610254355</v>
+        <v>2.796025101924146</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.460481491518614</v>
+        <v>-4.572755262948589</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.032319786044023</v>
+        <v>0.9874102774720326</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.04712328754232464</v>
+        <v>-0.0262492263413569</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.84514277949061</v>
+        <v>2.801119271160402</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.396802406287816</v>
+        <v>-4.507082704600258</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.056327400961014</v>
+        <v>1.012215281636037</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.1108023727731228</v>
+        <v>0.03942333200697395</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.881886211453761</v>
+        <v>2.839058786994072</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.325256083510939</v>
+        <v>-4.435536381823381</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.083437548111693</v>
+        <v>1.039325428786716</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.1108023727731228</v>
+        <v>0.03942333200697395</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.880377829493689</v>
+        <v>2.837550405034</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.28088295187237</v>
+        <v>-4.391163250184812</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.101049668202557</v>
+        <v>1.05693754887758</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.1551755044116914</v>
+        <v>0.08379646364554255</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.906864575912267</v>
+        <v>2.864037151452578</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.272928981577598</v>
+        <v>-4.38320927989004</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.104231256320465</v>
+        <v>1.060119136995489</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.1551755044116914</v>
+        <v>0.08379646364554255</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.906864575912267</v>
+        <v>2.864037151452578</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.225273251016542</v>
+        <v>-4.335553549328984</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.129675305572692</v>
+        <v>1.085563186247716</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.202831234972747</v>
+        <v>0.1314521942065982</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.941839771276705</v>
+        <v>2.899012346817016</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.097588941222246</v>
+        <v>-4.207869239534688</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.185641402865136</v>
+        <v>1.141529283540159</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.3305155447670435</v>
+        <v>0.2591365040008947</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.023342730528008</v>
+        <v>2.980515306068318</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.158255531624635</v>
+        <v>-4.268535829937077</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.148129439180053</v>
+        <v>1.104017319855075</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.2488172280485098</v>
+        <v>0.177438187282361</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.96107841297276</v>
+        <v>2.918250988513071</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.113417130016236</v>
+        <v>-4.223697428328679</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.170162502434041</v>
+        <v>1.126050383109063</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.2533606609933793</v>
+        <v>0.1819816202272305</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.96790217535031</v>
+        <v>2.925074750890621</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.214175765773234</v>
+        <v>-4.324456064085677</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.134019987762319</v>
+        <v>1.089907868437342</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.1645350922663739</v>
+        <v>0.09315605150022505</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.918767773745185</v>
+        <v>2.875940349285496</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.169972928687334</v>
+        <v>-4.280253226999776</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.157580725124516</v>
+        <v>1.11346860579954</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.2087379293522743</v>
+        <v>0.1373588885861255</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.951169078524562</v>
+        <v>2.908341654064873</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.206951956350776</v>
+        <v>-4.317232254663219</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.141199114528387</v>
+        <v>1.09708699520341</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.2457118311436048</v>
+        <v>0.174332790377456</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.971763420068608</v>
+        <v>2.928935995608919</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.227010035215617</v>
+        <v>-4.33729033352806</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.18442364816549</v>
+        <v>1.140311528840513</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.2457118311436048</v>
+        <v>0.174332790377456</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.023011185251648</v>
+        <v>2.980183760791959</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.187079362037727</v>
+        <v>-4.297359660350169</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.1988366220309</v>
+        <v>1.154724502705923</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.2856425043214952</v>
+        <v>0.2142634635553464</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.045410293752635</v>
+        <v>3.002582869292945</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.136047269315199</v>
+        <v>-4.246327567627642</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.214197687358181</v>
+        <v>1.170085568033204</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.3366745970440231</v>
+        <v>0.2652955562778743</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.070977777624422</v>
+        <v>3.028150353164733</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.070823088187994</v>
+        <v>-4.181103386500436</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.257474763901768</v>
+        <v>1.213362644576791</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.4018987781712288</v>
+        <v>0.3305197374050799</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.12729969039345</v>
+        <v>3.084472265933761</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.033396068116859</v>
+        <v>-4.143676366429302</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.268406544229502</v>
+        <v>1.224294424904525</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.4071503162004104</v>
+        <v>0.3357712754342616</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.126411585510239</v>
+        <v>3.08358416105055</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.053507724151568</v>
+        <v>-4.16378802246401</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.261618674146859</v>
+        <v>1.217506554821882</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.4181776611978296</v>
+        <v>0.3467986204316808</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.134284784839931</v>
+        <v>3.091457360380242</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.999762909724363</v>
+        <v>-4.110043208036806</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.443674370938951</v>
+        <v>1.399562251613975</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.4282409706382916</v>
+        <v>0.3568619298721428</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.300880541525419</v>
+        <v>3.25805311706573</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.975971341118221</v>
+        <v>-4.086251639430664</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.573303907599226</v>
+        <v>1.529191788274249</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.4520325392444339</v>
+        <v>0.3806534984782851</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.435268391906922</v>
+        <v>3.392440967447233</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.012725759679943</v>
+        <v>-4.123006057992386</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.550310116188396</v>
+        <v>1.506197996863418</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.4520325392444339</v>
+        <v>0.3806534984782851</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.426976367920781</v>
+        <v>3.384148943461092</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.008391456622894</v>
+        <v>-4.118671754935338</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.550237032994995</v>
+        <v>1.506124913670017</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.6036826425636378</v>
+        <v>0.5323036017974889</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.516159625496083</v>
+        <v>3.473332201036393</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.99949899522961</v>
+        <v>-4.109779293542055</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.5713484232791</v>
+        <v>1.527236303954122</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.6036826425636378</v>
+        <v>0.5323036017974889</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.533714031222874</v>
+        <v>3.490886606763185</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.167975112199487</v>
+        <v>-4.278255410511933</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.495813023895733</v>
+        <v>1.451700904570755</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.575734806847057</v>
+        <v>0.5043557660809082</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.50880037719751</v>
+        <v>3.46597295273782</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.233772154546119</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.470175583337904</v>
+        <v>-3.580455881650349</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.845345496897209</v>
+        <v>1.801233377572232</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.5053867474766462</v>
+        <v>0.4340077067104974</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.537004203032107</v>
+        <v>3.494176778572418</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.224436177043023</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.447454479654751</v>
+        <v>-3.557734777967197</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.845097960867375</v>
+        <v>1.800985841542397</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.5053867474766462</v>
+        <v>0.4340077067104974</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.527668225529011</v>
+        <v>3.484840801069322</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.383342302894192</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.587747079191944</v>
+        <v>-3.698027377504389</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.947887046903667</v>
+        <v>1.903774927578689</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.3650941479394536</v>
+        <v>0.2937151071733048</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.602398791657865</v>
+        <v>3.559571367198175</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.420420125387839</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.799872414931138</v>
+        <v>-3.852808384282644</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.900114735101636</v>
+        <v>1.878940347361034</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.3037382022901745</v>
+        <v>0.2603474331188287</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.602663046761944</v>
+        <v>3.576628585259136</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.900877010053618</v>
+        <v>3.575790493716756</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.637811418335678</v>
+        <v>3.332144778755734</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.799872414931138</v>
+        <v>-3.852808384282644</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.900114735101636</v>
+        <v>1.878940347361034</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.3037382022901745</v>
+        <v>0.2603474331188287</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.630875215322046</v>
+        <v>3.325208575742102</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240620.xlsx
+++ b/tame_output/ON/bt/strategyON_20240620.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>29.9%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>25.3%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.4%</t>
+          <t>-75.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.7%</t>
+          <t>109.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.2%</t>
+          <t>123.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.8%</t>
+          <t>94.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.2%</t>
+          <t>-71.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-546.9%</t>
+          <t>-570.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-84.5%</t>
+          <t>-47.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-188.3%</t>
+          <t>-194.3%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-18.7%</t>
+          <t>-22.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-16.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.3%</t>
+          <t>-185.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-198.0%</t>
+          <t>-221.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-113.5%</t>
+          <t>-109.8%</t>
         </is>
       </c>
     </row>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539463</v>
+        <v>3.501052558539464</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141699</v>
+        <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440632</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587859441027</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390584</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.691571733940719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812101</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646215</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611567</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626477</v>
+        <v>3.856161751626476</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.331682566110988</v>
+        <v>-8.291915294659031</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1742782265962788</v>
+        <v>-0.158371318015496</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.770793266080445</v>
+        <v>-1.731025994628489</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.096275264513597</v>
+        <v>2.120135627384771</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.182016175103474</v>
+        <v>-8.142248903651517</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1173038805062321</v>
+        <v>-0.1013969719254493</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.677889774837909</v>
+        <v>-1.638122503385953</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.14912514894616</v>
+        <v>2.172985511817333</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.049740701472587</v>
+        <v>-8.009973430020629</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.06902620430685014</v>
+        <v>-0.05311929572606733</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.545614301207022</v>
+        <v>-1.505847029755066</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.223857919871719</v>
+        <v>2.247718282742892</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.859141026799434</v>
+        <v>-7.819373755347477</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.01002872625004736</v>
+        <v>0.02593563483083017</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.35501462653387</v>
+        <v>-1.315247355081913</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.341032785363247</v>
+        <v>2.364893148234421</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.610141228115853</v>
+        <v>-7.570373956663896</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1225349869471386</v>
+        <v>0.1384418955279214</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.35501462653387</v>
+        <v>-1.315247355081913</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.353939126586906</v>
+        <v>2.377799489458079</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.715731217888957</v>
+        <v>-7.675963946437</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.04767693856132205</v>
+        <v>-0.03177002998053879</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.460604616306974</v>
+        <v>-1.420837344855018</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.162609203123824</v>
+        <v>2.186469565994998</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.734466120007554</v>
+        <v>-7.694698848555597</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.006626557531674404</v>
+        <v>0.009280351049108404</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.466200625967105</v>
+        <v>-1.426433354515149</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.207795939204832</v>
+        <v>2.231656302076006</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.586526078599955</v>
+        <v>-7.546758807147998</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.06732946365680226</v>
+        <v>-0.05142255507601945</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.445879710058548</v>
+        <v>-1.406112438606591</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.100109566061799</v>
+        <v>2.123969928932973</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.533556556345967</v>
+        <v>-7.493789284894009</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.05485564100868512</v>
+        <v>-0.03894873242790187</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.392910187804559</v>
+        <v>-1.353142916352602</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.123177293160714</v>
+        <v>2.147037656031888</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.490008149575276</v>
+        <v>-7.450240878123319</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.0443968903955021</v>
+        <v>-0.02848998181471885</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.392910187804559</v>
+        <v>-1.353142916352602</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.116216681065621</v>
+        <v>2.140077043936795</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.247859756121418</v>
+        <v>-7.208092484669461</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.06692482136718425</v>
+        <v>0.0828317299479675</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.392910187804559</v>
+        <v>-1.353142916352602</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.130679035446764</v>
+        <v>2.154539398317938</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.139600618998896</v>
+        <v>-7.099833347546939</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.104760596675388</v>
+        <v>0.1206675052561712</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.392910187804559</v>
+        <v>-1.353142916352602</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.125211155905959</v>
+        <v>2.149071518777133</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.016309484181765</v>
+        <v>-6.976542212729808</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1515751446128175</v>
+        <v>0.1674820531936003</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.269619052987428</v>
+        <v>-1.229851781535472</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.196683930806814</v>
+        <v>2.220544293677988</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.995160285278322</v>
+        <v>-6.955393013826365</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1677358024115199</v>
+        <v>0.1836427109923027</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.248469854083985</v>
+        <v>-1.208702582632029</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.217074428386205</v>
+        <v>2.240934791257379</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.751394843294878</v>
+        <v>-6.711627571842921</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2610226875519484</v>
+        <v>0.2769295961327312</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.248469854083985</v>
+        <v>-1.208702582632029</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.212855136733256</v>
+        <v>2.23671549960443</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.649632023017583</v>
+        <v>-6.609864751565626</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3038521295828822</v>
+        <v>0.319759038163665</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.235250785691556</v>
+        <v>-1.1954835142396</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.222910891688729</v>
+        <v>2.246771254559903</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.399781629068508</v>
+        <v>-6.360014357616551</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3965343621462143</v>
+        <v>0.4124412707269971</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.235250785691556</v>
+        <v>-1.1954835142396</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.215652966672431</v>
+        <v>2.239513329543605</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.223889536601076</v>
+        <v>-6.184122265149119</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4704903226538359</v>
+        <v>0.4863972312346188</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.235250785691556</v>
+        <v>-1.1954835142396</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.21925209019308</v>
+        <v>2.243112453064254</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.052443073578613</v>
+        <v>-6.012675802126656</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5523964139173749</v>
+        <v>0.5683033224981577</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.063804322669093</v>
+        <v>-1.024037051217137</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.335447474061112</v>
+        <v>2.359307836932286</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.978153507840274</v>
+        <v>-5.938386236388316</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5811327178290076</v>
+        <v>0.5970396264097904</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.9895147569307536</v>
+        <v>-0.9497474854787973</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.379041691120412</v>
+        <v>2.402902053991586</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.914517765606339</v>
+        <v>-5.874750494154382</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6112818157768984</v>
+        <v>0.6271887243576817</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.9258790146968191</v>
+        <v>-0.8861117432448627</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.421917937515091</v>
+        <v>2.445778300386264</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.803091006280419</v>
+        <v>-5.763323734828462</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6370467782910625</v>
+        <v>0.6529536868718453</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.9258790146968191</v>
+        <v>-0.8861117432448627</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.403112196298886</v>
+        <v>2.42697255917006</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.562660509475559</v>
+        <v>-5.522893238023602</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7349620536378838</v>
+        <v>0.7508689622186666</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.6854485178919588</v>
+        <v>-0.6456812464400025</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.549113571006679</v>
+        <v>2.572973933877853</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.490417941304364</v>
+        <v>-5.450650669852407</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7677883947411819</v>
+        <v>0.7836953033219647</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.6854485178919588</v>
+        <v>-0.6456812464400025</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.5530428848415</v>
+        <v>2.576903247712674</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.437419619022976</v>
+        <v>-5.397652347571019</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.789666307571077</v>
+        <v>0.8055732161518598</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.63011225889002</v>
+        <v>-0.5903449874380636</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.586923224160003</v>
+        <v>2.610783587031177</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.328614733543249</v>
+        <v>-5.288847462091292</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8301863329829615</v>
+        <v>0.8460932415637443</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.63011225889002</v>
+        <v>-0.5903449874380636</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.583921295379997</v>
+        <v>2.607781658251171</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.108593935506239</v>
+        <v>-5.068826664054281</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9197736892083799</v>
+        <v>0.9356805977891627</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4888924138220397</v>
+        <v>-0.4491251423700834</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.670232239431399</v>
+        <v>2.694092602302573</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539953</v>
+        <v>3.843274527539952</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.975726246442961</v>
+        <v>-4.935958974991004</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9888149476355141</v>
+        <v>1.004721856216297</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4888924138220397</v>
+        <v>-0.4491251423700834</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.686126422233222</v>
+        <v>2.709986785104396</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.855553163078462</v>
+        <v>-4.815785891626505</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.038030025421615</v>
+        <v>1.053936934002398</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.3687193304575408</v>
+        <v>-0.3289520590055844</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.759376116692223</v>
+        <v>2.783236479563397</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.710881017978725</v>
+        <v>-4.671113746526768</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.10598698602295</v>
+        <v>1.121893894603733</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.2240471853578034</v>
+        <v>-0.184279913905847</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.856267506313506</v>
+        <v>2.88012786918468</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.770755845336417</v>
+        <v>-4.73098857388446</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.068074546481299</v>
+        <v>1.083981455062082</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2839220127154955</v>
+        <v>-0.2441547412635391</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.806380101300316</v>
+        <v>2.83024046417149</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.683956347557409</v>
+        <v>-4.644189076105452</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.125194838915469</v>
+        <v>1.141101747496251</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.2839220127154955</v>
+        <v>-0.2441547412635391</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.828780594622883</v>
+        <v>2.852640957494056</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.686426054019215</v>
+        <v>-4.646658782567258</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.124279357704158</v>
+        <v>1.140186266284941</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.2863917191773017</v>
+        <v>-0.2466244477253453</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.827371172119211</v>
+        <v>2.851231534990385</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.754796240343225</v>
+        <v>-4.715028968891268</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.107938205649256</v>
+        <v>1.123845114230039</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.2771160201410867</v>
+        <v>-0.2373487486891304</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.843943514015642</v>
+        <v>2.867803876886815</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.863334421259359</v>
+        <v>-4.823567149807402</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.054959641914694</v>
+        <v>1.070866550495477</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.2771160201410867</v>
+        <v>-0.2373487486891304</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.834380222647533</v>
+        <v>2.858240585518707</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.894327580588064</v>
+        <v>-4.854560309136107</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8672719432235987</v>
+        <v>0.8831788518043815</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.2771160201410867</v>
+        <v>-0.2373487486891304</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.65908978768792</v>
+        <v>2.682950150559094</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.718853320795596</v>
+        <v>-4.679086049343638</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9420288791323739</v>
+        <v>0.9579357877131569</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.2771160201410867</v>
+        <v>-0.2373487486891304</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.663657019679708</v>
+        <v>2.687517382550881</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.829789573436845</v>
+        <v>-4.790022301984887</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8733964068370814</v>
+        <v>0.8893033154178642</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.2771160201410867</v>
+        <v>-0.2373487486891304</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.639399048440915</v>
+        <v>2.663259411312088</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.796126027964562</v>
+        <v>-4.756358756512605</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8899932102458998</v>
+        <v>0.9059001188266826</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2434524746688049</v>
+        <v>-0.2036852032168485</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.662728560944189</v>
+        <v>2.686588923815363</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.736273408760839</v>
+        <v>-4.696506137308882</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9241066443595214</v>
+        <v>0.9400135529403044</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.2434524746688049</v>
+        <v>-0.2036852032168485</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.672900947376322</v>
+        <v>2.696761310247496</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.650029945734461</v>
+        <v>-4.610262674282504</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9535503001439329</v>
+        <v>0.9694572087247157</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.2434524746688049</v>
+        <v>-0.2036852032168485</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.667847217950182</v>
+        <v>2.691707580821356</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.695336765133441</v>
+        <v>-4.655569493681484</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9272033478288666</v>
+        <v>0.9431102564096494</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2842626376780357</v>
+        <v>-0.2444953662260793</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.635136895589169</v>
+        <v>2.658997258460343</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.724369869835742</v>
+        <v>-4.684602598383785</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9161419789810477</v>
+        <v>0.9320488875618305</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2842626376780357</v>
+        <v>-0.2444953662260793</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.635688768622271</v>
+        <v>2.659549131493445</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.631559388384883</v>
+        <v>-4.591792116932925</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8825388634527571</v>
+        <v>0.8984457720335399</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1914521562271763</v>
+        <v>-0.15168488477522</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.620647749384152</v>
+        <v>2.644508112255326</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.67594885771431</v>
+        <v>-4.636181586262353</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8666565516455869</v>
+        <v>0.8825634602263699</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.235841625556604</v>
+        <v>-0.1960743541046476</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.595887543711096</v>
+        <v>2.61974790658227</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.56327763947806</v>
+        <v>-4.523510368026103</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9068007474518101</v>
+        <v>0.9227076560325929</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.1231704073203538</v>
+        <v>-0.08340313586839743</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.658565983164569</v>
+        <v>2.682426346035743</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.450900638295387</v>
+        <v>-4.41113336684343</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9572428437555465</v>
+        <v>0.9731497523363293</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.1231704073203538</v>
+        <v>-0.08340313586839743</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.664057278995236</v>
+        <v>2.68791764186641</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.47868103619674</v>
+        <v>-4.438913764744782</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9576278863635443</v>
+        <v>0.9735347949443274</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1509508052217068</v>
+        <v>-0.1111835337697505</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.658886242022964</v>
+        <v>2.682746604894138</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.561682317222019</v>
+        <v>-4.521915045770061</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7627830939540861</v>
+        <v>0.7786900025348691</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1695216897488806</v>
+        <v>-0.1297544182969242</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.486099431307313</v>
+        <v>2.509959794178487</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.67029639566535</v>
+        <v>-4.630529124213393</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8394871232959593</v>
+        <v>0.8553940318767421</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1695216897488806</v>
+        <v>-0.1297544182969242</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.606249092026518</v>
+        <v>2.630109454897692</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.756894978646453</v>
+        <v>-4.717127707194495</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8193607162058412</v>
+        <v>0.835267624786624</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1695216897488806</v>
+        <v>-0.1297544182969242</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.620762118128841</v>
+        <v>2.644622481000015</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.718511316088302</v>
+        <v>-4.678744044636344</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8321336225714702</v>
+        <v>0.8480405311522532</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.1311380271907294</v>
+        <v>-0.09137075573877307</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.641211757006101</v>
+        <v>2.665072119877275</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.541394986053136</v>
+        <v>-4.501627714601178</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8997091834308386</v>
+        <v>0.9156160920116214</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.1311380271907294</v>
+        <v>-0.09137075573877307</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.637940785851403</v>
+        <v>2.661801148722577</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.586487230886681</v>
+        <v>-4.546719959434724</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8823556772593335</v>
+        <v>0.8982625858401163</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1930340703601192</v>
+        <v>-0.1532667989081629</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.601486551711682</v>
+        <v>2.625346914582856</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.407111809647914</v>
+        <v>-4.367344538195956</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9478928210612549</v>
+        <v>0.9637997296420378</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.03625731218940054</v>
+        <v>0.003509959262555817</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.689339581920528</v>
+        <v>2.713199944791701</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.452126023168519</v>
+        <v>-4.412358751716562</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9106945909846023</v>
+        <v>0.9266014995653853</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.06660620750400514</v>
+        <v>-0.02683893605204879</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.651937700063355</v>
+        <v>2.675798062934528</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.719130533440954</v>
+        <v>-4.679363261988997</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.809584349214574</v>
+        <v>0.825491257795357</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2609692455469537</v>
+        <v>-0.2212019740949974</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.541011439576531</v>
+        <v>2.564871802447705</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.820328314878127</v>
+        <v>-4.78056104342617</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7683091585362063</v>
+        <v>0.7842160671169893</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3293780590922729</v>
+        <v>-0.2896107876403166</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.499170073345841</v>
+        <v>2.523030436217015</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.787852728707355</v>
+        <v>-4.748085457255398</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7788993545588321</v>
+        <v>0.7948062631396149</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3293780590922729</v>
+        <v>-0.2896107876403166</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.496770034900158</v>
+        <v>2.520630397771332</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.768814601000058</v>
+        <v>-4.7290473295481</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7830393248499958</v>
+        <v>0.7989462334307786</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3875616704234675</v>
+        <v>-0.3477943989715111</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.458384587309686</v>
+        <v>2.48224495018086</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.799941232150676</v>
+        <v>-4.760173960698719</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9481705413284289</v>
+        <v>0.964077449909212</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3875616704234675</v>
+        <v>-0.3477943989715111</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.635966456248366</v>
+        <v>2.65982681911954</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.813807993484594</v>
+        <v>-4.774040722032637</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9434571657809954</v>
+        <v>0.9593640743617784</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4254195871572904</v>
+        <v>-0.385652315705334</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.614085035194206</v>
+        <v>2.63794539806538</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.834065292013552</v>
+        <v>-4.794298020561595</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9413627767663382</v>
+        <v>0.957269685347121</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4254195871572904</v>
+        <v>-0.385652315705334</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.620093565591132</v>
+        <v>2.643953928462306</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.686322321778549</v>
+        <v>-4.646555050326592</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.079612612652361</v>
+        <v>1.095519521233144</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2576122299224072</v>
+        <v>-0.2178449584704509</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.799930627724084</v>
+        <v>2.823790990595258</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.788337004309771</v>
+        <v>-4.748569732857813</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.041600361171354</v>
+        <v>1.057507269752136</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2576122299224072</v>
+        <v>-0.2178449584704509</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.802724249255565</v>
+        <v>2.826584612126739</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.782184298256986</v>
+        <v>-4.742417026805029</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.044723791984126</v>
+        <v>1.060630700564908</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.2514595238696229</v>
+        <v>-0.2116922524176666</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.807078221278894</v>
+        <v>2.830938584150068</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.957034412340778</v>
+        <v>2.993044333682986</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.798993596407488</v>
+        <v>-4.759226324955531</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.037080549464035</v>
+        <v>1.088997379387027</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.2682688220201246</v>
+        <v>-0.2285015505681682</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.796073119128703</v>
+        <v>2.855943403342086</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.023369966137599</v>
+        <v>3.059379887479807</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.736695597631366</v>
+        <v>-4.696928326179409</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.128335302771305</v>
+        <v>1.180252132694297</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.2682688220201246</v>
+        <v>-0.2285015505681682</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.862408672925524</v>
+        <v>2.922278957138907</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992194</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.731950838526997</v>
+        <v>2.767960759869205</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.534905399966208</v>
+        <v>-4.495138128514251</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9176322542267661</v>
+        <v>0.9695490841497578</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.07025062985097019</v>
+        <v>-0.03048335839901384</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.689800460616415</v>
+        <v>2.749670744829797</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.802241070849172</v>
+        <v>2.838250992191381</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.475014718323615</v>
+        <v>-4.435247446871657</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.011878759205979</v>
+        <v>1.06379558912897</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.01035994820837671</v>
+        <v>0.02940732324357964</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.796025101924146</v>
+        <v>2.855895386137528</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319549</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.816868806965215</v>
+        <v>2.852878728307424</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.572755262948589</v>
+        <v>-4.532987991496632</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9874102774720326</v>
+        <v>1.039327107395024</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.0262492263413569</v>
+        <v>0.01351804511059945</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.801119271160402</v>
+        <v>2.860989555373784</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489388</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.815404787789887</v>
+        <v>2.851414709132096</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.507082704600258</v>
+        <v>-4.709325751619561</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.012215281636037</v>
+        <v>0.9673279841705242</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.03942333200697395</v>
+        <v>-0.1628197150123299</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.839058786994072</v>
+        <v>2.753722880124698</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397798</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.813896405829816</v>
+        <v>2.849906327172024</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.435536381823381</v>
+        <v>-4.637779428842684</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.039325428786716</v>
+        <v>0.9944381313212034</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.03942333200697395</v>
+        <v>-0.1628197150123299</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.837550405034</v>
+        <v>2.752214498164627</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.836023391024965</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.813759273265252</v>
+        <v>2.849769194607461</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.391163250184812</v>
+        <v>-4.593406297204115</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.05693754887758</v>
+        <v>1.012050251412067</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.08379646364554255</v>
+        <v>-0.1184465833737613</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.864037151452578</v>
+        <v>2.778701244583204</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821591150863226</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.813759273265252</v>
+        <v>2.849769194607461</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.38320927989004</v>
+        <v>-4.585452326909343</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.060119136995489</v>
+        <v>1.015231839529976</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.08379646364554255</v>
+        <v>-0.1184465833737613</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.864037151452578</v>
+        <v>2.778701244583204</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833040181947585</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.820141030293057</v>
+        <v>2.856150951635265</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.335553549328984</v>
+        <v>-4.537796596348287</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.085563186247716</v>
+        <v>1.040675888782203</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.1314521942065982</v>
+        <v>-0.0707908528127057</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.899012346817016</v>
+        <v>2.813676439947642</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822707244326877</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.825033403667781</v>
+        <v>2.86104332500999</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.207869239534688</v>
+        <v>-4.410112286553991</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.141529283540159</v>
+        <v>1.096641986074646</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.2591365040008947</v>
+        <v>0.05689345698159076</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.980515306068318</v>
+        <v>2.895179399198945</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828837911314553</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.811788076143654</v>
+        <v>2.847797997485862</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.268535829937077</v>
+        <v>-4.470778876956381</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.104017319855075</v>
+        <v>1.059130022389563</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.177438187282361</v>
+        <v>-0.02480485973694291</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.918250988513071</v>
+        <v>2.832915081643697</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816866067690029</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.815885778754282</v>
+        <v>2.851895700096491</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.223697428328679</v>
+        <v>-4.425940475347982</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.126050383109063</v>
+        <v>1.081163085643551</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.1819816202272305</v>
+        <v>-0.02026142679207343</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.925074750890621</v>
+        <v>2.839738844021247</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817961388674313</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.82004671838536</v>
+        <v>2.856056639727569</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.324456064085677</v>
+        <v>-4.52669911110498</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.089907868437342</v>
+        <v>1.045020570971829</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.09315605150022505</v>
+        <v>-0.1090869955190789</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.875940349285496</v>
+        <v>2.790604442416122</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.826713779163222</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.825926320913197</v>
+        <v>2.861936242255406</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.280253226999776</v>
+        <v>-4.48249627401908</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.11346860579954</v>
+        <v>1.068581308334027</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.1373588885861255</v>
+        <v>-0.06488415843317841</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.908341654064873</v>
+        <v>2.823005747195499</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838228663022907</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.824336321382445</v>
+        <v>2.860346242724654</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.317232254663219</v>
+        <v>-4.519475301682522</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.09708699520341</v>
+        <v>1.052199697737897</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.174332790377456</v>
+        <v>-0.02791025664184787</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.928935995608919</v>
+        <v>2.843600088739545</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.863924114042141</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.875584086565484</v>
+        <v>2.911594007907693</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.33729033352806</v>
+        <v>-4.539533380547363</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.140311528840513</v>
+        <v>1.095424231375001</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.174332790377456</v>
+        <v>-0.02791025664184787</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.980183760791959</v>
+        <v>2.894847853922585</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47226,19 @@
         <v>3.865367715078284</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.874024791159738</v>
+        <v>2.910034712501946</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.297359660350169</v>
+        <v>-4.499602707369473</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.154724502705923</v>
+        <v>1.10983720524041</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.2142634635553464</v>
+        <v>0.01202041653604247</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.002582869292945</v>
+        <v>2.917246962423572</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47249,19 @@
         <v>3.864518876232401</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.868973019398008</v>
+        <v>2.904982940740216</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.246327567627642</v>
+        <v>-4.448570614646945</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.170085568033204</v>
+        <v>1.125198270567691</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.2652955562778743</v>
+        <v>0.06305250925857042</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.028150353164733</v>
+        <v>2.942814446295359</v>
       </c>
     </row>
     <row r="1988">
@@ -47272,19 +47272,19 @@
         <v>3.842576394162116</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.886160423490713</v>
+        <v>2.922170344832921</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.181103386500436</v>
+        <v>-4.38334643351974</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.213362644576791</v>
+        <v>1.168475347111278</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.3305197374050799</v>
+        <v>0.128276690385776</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.084472265933761</v>
+        <v>2.999136359064387</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.84009022063982</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.882121395789993</v>
+        <v>2.918131317132202</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.143676366429302</v>
+        <v>-4.345919413448605</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.224294424904525</v>
+        <v>1.179407127439012</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.3357712754342616</v>
+        <v>0.1335282284149577</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.08358416105055</v>
+        <v>2.998248254181176</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.845198842749925</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.883378188121233</v>
+        <v>2.919388109463442</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.16378802246401</v>
+        <v>-4.366031069483314</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.217506554821882</v>
+        <v>1.172619257356369</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.3467986204316808</v>
+        <v>0.1445555734123769</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.091457360380242</v>
+        <v>3.006121453510868</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393552</v>
+        <v>3.828690479393551</v>
       </c>
       <c r="C1991" t="n">
-        <v>3.043935959142444</v>
+        <v>3.079945880484653</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.110043208036806</v>
+        <v>-4.312286255056109</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.399562251613975</v>
+        <v>1.354674954148462</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.3568619298721428</v>
+        <v>0.1546188828528389</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.25805311706573</v>
+        <v>3.172717210196356</v>
       </c>
     </row>
     <row r="1992">
@@ -47364,19 +47364,19 @@
         <v>3.813251854714889</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.164048868360261</v>
+        <v>3.20005878970247</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.086251639430664</v>
+        <v>-4.325151999751778</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.529191788274249</v>
+        <v>1.469641565488011</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.3806534984782851</v>
+        <v>0.1417531381571694</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.392440967447233</v>
+        <v>3.285110672596772</v>
       </c>
     </row>
     <row r="1993">
@@ -47387,19 +47387,19 @@
         <v>3.814259761756015</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.15575684437412</v>
+        <v>3.191766765716329</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.123006057992386</v>
+        <v>-4.361906418313501</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.506197996863418</v>
+        <v>1.446647774077181</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.3806534984782851</v>
+        <v>0.1417531381571694</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.384148943461092</v>
+        <v>3.276818648610631</v>
       </c>
     </row>
     <row r="1994">
@@ -47410,19 +47410,19 @@
         <v>3.803426852654189</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.1539500399579</v>
+        <v>3.189959961300108</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.118671754935338</v>
+        <v>-4.357572115256453</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.506124913670017</v>
+        <v>1.44657469088378</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.5323036017974889</v>
+        <v>0.2934032414763733</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.473332201036393</v>
+        <v>3.366001906185933</v>
       </c>
     </row>
     <row r="1995">
@@ -47433,19 +47433,19 @@
         <v>3.79629317771712</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.171504445684691</v>
+        <v>3.2075143670269</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.109779293542055</v>
+        <v>-4.34867965386317</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.527236303954122</v>
+        <v>1.467686081167885</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.5323036017974889</v>
+        <v>0.2934032414763733</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.490886606763185</v>
+        <v>3.383556311912724</v>
       </c>
     </row>
     <row r="1996">
@@ -47456,19 +47456,19 @@
         <v>3.794453975702628</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.163359493089275</v>
+        <v>3.199369414431484</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.278255410511933</v>
+        <v>-4.517155770833047</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.451700904570755</v>
+        <v>1.392150681784518</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.5043557660809082</v>
+        <v>0.2654554057597925</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.46597295273782</v>
+        <v>3.358642657887359</v>
       </c>
     </row>
     <row r="1997">
@@ -47479,19 +47479,19 @@
         <v>3.795603100539971</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.233772154546119</v>
+        <v>3.269782075888327</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.580455881650349</v>
+        <v>-3.819356241971464</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.801233377572232</v>
+        <v>1.741683154785995</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.4340077067104974</v>
+        <v>0.1951073463893818</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.494176778572418</v>
+        <v>3.386846483721957</v>
       </c>
     </row>
     <row r="1998">
@@ -47502,19 +47502,19 @@
         <v>3.784700379389901</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.224436177043023</v>
+        <v>3.260446098385232</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.557734777967197</v>
+        <v>-3.796635138288311</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.800985841542397</v>
+        <v>1.74143561875616</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.4340077067104974</v>
+        <v>0.1951073463893818</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.484840801069322</v>
+        <v>3.377510506218861</v>
       </c>
     </row>
     <row r="1999">
@@ -47525,19 +47525,19 @@
         <v>3.783234730534939</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.383342302894192</v>
+        <v>3.419352224236401</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.698027377504389</v>
+        <v>-3.936927737825504</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.903774927578689</v>
+        <v>1.844224704792452</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.2937151071733048</v>
+        <v>0.05481474685218918</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.559571367198175</v>
+        <v>3.452241072347715</v>
       </c>
     </row>
     <row r="2000">
@@ -47548,19 +47548,19 @@
         <v>3.779962759401677</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.420420125387839</v>
+        <v>3.456430046730048</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.852808384282644</v>
+        <v>-4.091708744603759</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.878940347361034</v>
+        <v>1.819390124574797</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.2603474331188287</v>
+        <v>0.02144707279771307</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.576628585259136</v>
+        <v>3.469298290408676</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.575790493716756</v>
+        <v>3.579534779650182</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.332144778755734</v>
+        <v>3.368866080424836</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.852808384282644</v>
+        <v>-4.091708744603759</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.878940347361034</v>
+        <v>1.819390124574797</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.2603474331188287</v>
+        <v>0.02144707279771307</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.325208575742102</v>
+        <v>3.361929877411204</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240620.xlsx
+++ b/tame_output/ON/bt/strategyON_20240620.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>55.1%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>76.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>60.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,22 +859,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>36.9%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.6%</t>
+          <t>-75.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.1%</t>
+          <t>109.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.5%</t>
+          <t>123.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.6%</t>
+          <t>-51.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.5%</t>
+          <t>-70.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>451.2%</t>
+          <t>454.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-570.7%</t>
+          <t>-559.7%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.2%</t>
+          <t>-40.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-47.0%</t>
+          <t>-33.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-194.3%</t>
+          <t>-193.5%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-22.5%</t>
+          <t>-20.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.6%</t>
+          <t>-32.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>-13.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>-97.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-185.7%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-221.8%</t>
+          <t>-210.8%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>95.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.1%</t>
+          <t>-27.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-109.8%</t>
+          <t>-98.2%</t>
         </is>
       </c>
     </row>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539464</v>
+        <v>3.501052558539463</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.69855614979376</v>
+        <v>-9.624990596265652</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7449719890946467</v>
+        <v>-0.7155457676834036</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.094282449957284</v>
+        <v>-2.020716896429177</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.878237425162234</v>
+        <v>1.922376757279099</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.902814325123623</v>
+        <v>-9.829248771595516</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8211620621079496</v>
+        <v>-0.791735840696707</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.221921394571273</v>
+        <v>-2.148355841043166</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.807167255512484</v>
+        <v>1.851306587629348</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.977147301383788</v>
+        <v>-9.90358174785568</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8464126981275792</v>
+        <v>-0.8169864767163366</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.366620918505946</v>
+        <v>-2.293055364977838</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.724830095636116</v>
+        <v>1.76896942775298</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.903677469716339</v>
+        <v>-9.830111916188232</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8016530639671786</v>
+        <v>-0.772226842555936</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.293151086838497</v>
+        <v>-2.21958553331039</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.784283696130006</v>
+        <v>1.828423028246871</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.07880188710288</v>
+        <v>-10.00523633357477</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8571476101742794</v>
+        <v>-0.8277213887630364</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.468275504225041</v>
+        <v>-2.394709950696934</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.693764266445597</v>
+        <v>1.737903598562461</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.31325398111737</v>
+        <v>-10.23968842758926</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9581476126816715</v>
+        <v>-0.9287213912704284</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.468275504225041</v>
+        <v>-2.394709950696934</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.686545101544001</v>
+        <v>1.730684433660865</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.41762871214382</v>
+        <v>-10.34406315861571</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.006569695866226</v>
+        <v>-0.9771434744549832</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.572650235251487</v>
+        <v>-2.499084681723379</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.617248072154157</v>
+        <v>1.661387404271021</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.47041486774414</v>
+        <v>-10.39684931421604</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.0265683682678</v>
+        <v>-0.9971421468565573</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.668325721833884</v>
+        <v>-2.594760168305776</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.560958570043275</v>
+        <v>1.605097902160139</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.59645166111243</v>
+        <v>-10.52288610758433</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.074289356986001</v>
+        <v>-1.044863135574758</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.643074099024141</v>
+        <v>-2.569508545496034</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.578803272358235</v>
+        <v>1.6229426044751</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.54443614714362</v>
+        <v>-10.47087059361551</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.049492815712076</v>
+        <v>-1.020066594300832</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.643074099024141</v>
+        <v>-2.569508545496034</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.582793608044636</v>
+        <v>1.6269329401615</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.68610798886774</v>
+        <v>-10.61254243533963</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.107636779300465</v>
+        <v>-1.078210557889222</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.643074099024141</v>
+        <v>-2.569508545496034</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.581318381145894</v>
+        <v>1.625457713262759</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.63651714444291</v>
+        <v>-10.5629515909148</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.072747031365659</v>
+        <v>-1.043320809954416</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.593483254599307</v>
+        <v>-2.5199177010712</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.626126297965667</v>
+        <v>1.670265630082531</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.62370975143813</v>
+        <v>-10.55014419791003</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.080675207810433</v>
+        <v>-1.05124898639919</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.642339029608209</v>
+        <v>-2.568773476080101</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.583761699313643</v>
+        <v>1.627901031430508</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.39786459871872</v>
+        <v>-10.32429904519061</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.9807580736864598</v>
+        <v>-0.9513318522752159</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.600412354021045</v>
+        <v>-2.526846800492938</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.61849677770215</v>
+        <v>1.662636109819015</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.27328594238113</v>
+        <v>-10.19972038885302</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9297874665953638</v>
+        <v>-0.9003612451841208</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.600412354021045</v>
+        <v>-2.526846800492938</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.619635922258209</v>
+        <v>1.663775254375073</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.32618123042542</v>
+        <v>-10.25261567689731</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9483118076509713</v>
+        <v>-0.9188855862397274</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.595457007932599</v>
+        <v>-2.521891454404491</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.625242904073384</v>
+        <v>1.669382236190249</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.25404805513754</v>
+        <v>-10.18048250160943</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9137248332971817</v>
+        <v>-0.8842986118859386</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.595457007932599</v>
+        <v>-2.521891454404491</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.630976608312021</v>
+        <v>1.675115940428885</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.18268166252789</v>
+        <v>-10.10911610899978</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8949155386471883</v>
+        <v>-0.8654893172359444</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.524090615322951</v>
+        <v>-2.450525061794843</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.664059181483945</v>
+        <v>1.708198513600809</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.08922262854266</v>
+        <v>-10.01565707501456</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8674154063660064</v>
+        <v>-0.8379891849547625</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.524090615322951</v>
+        <v>-2.450525061794843</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.654175700171037</v>
+        <v>1.698315032287901</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.821980827674267</v>
+        <v>-9.748415274146158</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7623532465180207</v>
+        <v>-0.7329270251067772</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.524090615322951</v>
+        <v>-2.450525061794843</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.652341139671663</v>
+        <v>1.696480471788528</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.724073788997776</v>
+        <v>-9.650508235469667</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7234907460208855</v>
+        <v>-0.6940645246096415</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.456104865462394</v>
+        <v>-2.382539311934287</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.692832274614536</v>
+        <v>1.736971606731401</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.700120248021818</v>
+        <v>-9.626554694493709</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7132408234850085</v>
+        <v>-0.683814602073765</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.432151324486437</v>
+        <v>-2.358585770958329</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.707872905345605</v>
+        <v>1.752012237462469</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.436060309699021</v>
+        <v>-9.362494756170912</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6208771643176418</v>
+        <v>-0.5914509429063983</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.168091386163641</v>
+        <v>-2.094525832635533</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.85304855217753</v>
+        <v>1.897187884294394</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.728980686194184</v>
+        <v>-8.655415132666075</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3408323485760079</v>
+        <v>-0.3114061271647643</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.168091386163641</v>
+        <v>-2.094525832635533</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.850261518517229</v>
+        <v>1.894400850634093</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.688796387827994</v>
+        <v>-8.615230834299885</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3244150053416903</v>
+        <v>-0.2949887839304468</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.12790708779745</v>
+        <v>-2.054341534269343</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.874715721424785</v>
+        <v>1.918855053541649</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.52539651688863</v>
+        <v>-8.451830963360521</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.259688235745188</v>
+        <v>-0.2302620143339444</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.964507216858087</v>
+        <v>-1.89094166332998</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.972122465209159</v>
+        <v>2.016261797326024</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.291915294659031</v>
+        <v>-8.218349741130922</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.158371318015496</v>
+        <v>-0.1289450966042525</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.731025994628489</v>
+        <v>-1.657460441100381</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.120135627384771</v>
+        <v>2.164274959501635</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.142248903651517</v>
+        <v>-8.068683350123408</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1013969719254493</v>
+        <v>-0.07197075051420576</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.638122503385953</v>
+        <v>-1.564556949857846</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.172985511817333</v>
+        <v>2.217124843934198</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.009973430020629</v>
+        <v>-7.936407876492521</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.05311929572606733</v>
+        <v>-0.02369307431482426</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.505847029755066</v>
+        <v>-1.432281476226959</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.247718282742892</v>
+        <v>2.291857614859757</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.819373755347477</v>
+        <v>-7.745808201819369</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.02593563483083017</v>
+        <v>0.05536185624207368</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.315247355081913</v>
+        <v>-1.241681801553806</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.364893148234421</v>
+        <v>2.409032480351285</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.570373956663896</v>
+        <v>-7.496808403135788</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1384418955279214</v>
+        <v>0.1678681169391649</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.315247355081913</v>
+        <v>-1.241681801553806</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.377799489458079</v>
+        <v>2.421938821574944</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.675963946437</v>
+        <v>-7.602398392908892</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.03177002998053879</v>
+        <v>-0.002343808569295724</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.420837344855018</v>
+        <v>-1.34727179132691</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.186469565994998</v>
+        <v>2.230608898111862</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.694698848555597</v>
+        <v>-7.621133295027489</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.009280351049108404</v>
+        <v>0.03870657246035192</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.426433354515149</v>
+        <v>-1.352867800987042</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.231656302076006</v>
+        <v>2.27579563419287</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.546758807147998</v>
+        <v>-7.47319325361989</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.05142255507601945</v>
+        <v>-0.02199633366477594</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.406112438606591</v>
+        <v>-1.332546885078484</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.123969928932973</v>
+        <v>2.168109261049837</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.493789284894009</v>
+        <v>-7.420223731365901</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.03894873242790187</v>
+        <v>-0.009522511016658797</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.353142916352602</v>
+        <v>-1.279577362824495</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.147037656031888</v>
+        <v>2.191176988148752</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.450240878123319</v>
+        <v>-7.376675324595211</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.02848998181471885</v>
+        <v>0.0009362395965242243</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.353142916352602</v>
+        <v>-1.279577362824495</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.140077043936795</v>
+        <v>2.184216376053659</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.208092484669461</v>
+        <v>-7.134526931141353</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.0828317299479675</v>
+        <v>0.1122579513592106</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.353142916352602</v>
+        <v>-1.279577362824495</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.154539398317938</v>
+        <v>2.198678730434802</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.099833347546939</v>
+        <v>-7.026267794018831</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1206675052561712</v>
+        <v>0.1500937266674143</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.353142916352602</v>
+        <v>-1.279577362824495</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.149071518777133</v>
+        <v>2.193210850893997</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.976542212729808</v>
+        <v>-6.9029766592017</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1674820531936003</v>
+        <v>0.1969082746048434</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.229851781535472</v>
+        <v>-1.156286228007365</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.220544293677988</v>
+        <v>2.264683625794852</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.955393013826365</v>
+        <v>-6.881827460298257</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1836427109923027</v>
+        <v>0.2130689324035462</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.208702582632029</v>
+        <v>-1.135137029103921</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.240934791257379</v>
+        <v>2.285074123374244</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.711627571842921</v>
+        <v>-6.638062018314812</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2769295961327312</v>
+        <v>0.3063558175439742</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.208702582632029</v>
+        <v>-1.135137029103921</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.23671549960443</v>
+        <v>2.280854831721294</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.609864751565626</v>
+        <v>-6.536299198037518</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.319759038163665</v>
+        <v>0.3491852595749085</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.1954835142396</v>
+        <v>-1.121917960711493</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.246771254559903</v>
+        <v>2.290910586676767</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.360014357616551</v>
+        <v>-6.286448804088443</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4124412707269971</v>
+        <v>0.4418674921382402</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.1954835142396</v>
+        <v>-1.121917960711493</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.239513329543605</v>
+        <v>2.28365266166047</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.184122265149119</v>
+        <v>-6.11055671162101</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4863972312346188</v>
+        <v>0.5158234526458623</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.1954835142396</v>
+        <v>-1.121917960711493</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.243112453064254</v>
+        <v>2.287251785181118</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.012675802126656</v>
+        <v>-5.939110248598547</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5683033224981577</v>
+        <v>0.5977295439094013</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.024037051217137</v>
+        <v>-0.9504714976890295</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.359307836932286</v>
+        <v>2.40344716904915</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.938386236388316</v>
+        <v>-5.864820682860207</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5970396264097904</v>
+        <v>0.6264658478210339</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.9497474854787973</v>
+        <v>-0.8761819319506903</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.402902053991586</v>
+        <v>2.447041386108451</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.874750494154382</v>
+        <v>-5.801184940626273</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6271887243576817</v>
+        <v>0.6566149457689252</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8861117432448627</v>
+        <v>-0.8125461897167557</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.445778300386264</v>
+        <v>2.489917632503128</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.763323734828462</v>
+        <v>-5.689758181300353</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6529536868718453</v>
+        <v>0.6823799082830888</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8861117432448627</v>
+        <v>-0.8125461897167557</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.42697255917006</v>
+        <v>2.471111891286924</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.522893238023602</v>
+        <v>-5.449327684495493</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7508689622186666</v>
+        <v>0.7802951836299101</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.6456812464400025</v>
+        <v>-0.5721156929118955</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.572973933877853</v>
+        <v>2.617113265994718</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.450650669852407</v>
+        <v>-5.377085116324298</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7836953033219647</v>
+        <v>0.8131215247332082</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.6456812464400025</v>
+        <v>-0.5721156929118955</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.576903247712674</v>
+        <v>2.621042579829538</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.397652347571019</v>
+        <v>-5.32408679404291</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8055732161518598</v>
+        <v>0.8349994375631034</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5903449874380636</v>
+        <v>-0.5167794339099566</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.610783587031177</v>
+        <v>2.654922919148041</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.288847462091292</v>
+        <v>-5.215281908563183</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8460932415637443</v>
+        <v>0.8755194629749878</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5903449874380636</v>
+        <v>-0.5167794339099566</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.607781658251171</v>
+        <v>2.651920990368035</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.068826664054281</v>
+        <v>-4.995261110526172</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9356805977891627</v>
+        <v>0.9651068192004062</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4491251423700834</v>
+        <v>-0.3755595888419764</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.694092602302573</v>
+        <v>2.738231934419437</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.935958974991004</v>
+        <v>-4.862393421462895</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.004721856216297</v>
+        <v>1.03414807762754</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4491251423700834</v>
+        <v>-0.3755595888419764</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.709986785104396</v>
+        <v>2.75412611722126</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.815785891626505</v>
+        <v>-4.742220338098396</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.053936934002398</v>
+        <v>1.083363155413642</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.3289520590055844</v>
+        <v>-0.2553865054774774</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.783236479563397</v>
+        <v>2.827375811680261</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.671113746526768</v>
+        <v>-4.597548192998659</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.121893894603733</v>
+        <v>1.151320116014977</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.184279913905847</v>
+        <v>-0.11071436037774</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.88012786918468</v>
+        <v>2.924267201301544</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.73098857388446</v>
+        <v>-4.657423020356351</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.083981455062082</v>
+        <v>1.113407676473326</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2441547412635391</v>
+        <v>-0.1705891877354321</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.83024046417149</v>
+        <v>2.874379796288354</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.644189076105452</v>
+        <v>-4.570623522577343</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.141101747496251</v>
+        <v>1.170527968907495</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.2441547412635391</v>
+        <v>-0.1705891877354321</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.852640957494056</v>
+        <v>2.89678028961092</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.646658782567258</v>
+        <v>-4.573093229039149</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.140186266284941</v>
+        <v>1.169612487696185</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.2466244477253453</v>
+        <v>-0.1730588941972383</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.851231534990385</v>
+        <v>2.895370867107249</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.715028968891268</v>
+        <v>-4.641463415363159</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.123845114230039</v>
+        <v>1.153271335641283</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.2373487486891304</v>
+        <v>-0.1637831951610234</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.867803876886815</v>
+        <v>2.91194320900368</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.823567149807402</v>
+        <v>-4.750001596279293</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.070866550495477</v>
+        <v>1.10029277190672</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.2373487486891304</v>
+        <v>-0.1637831951610234</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.858240585518707</v>
+        <v>2.902379917635571</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.854560309136107</v>
+        <v>-4.780994755607998</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8831788518043815</v>
+        <v>0.9126050732156252</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.2373487486891304</v>
+        <v>-0.1637831951610234</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.682950150559094</v>
+        <v>2.727089482675958</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.679086049343638</v>
+        <v>-4.605520495815529</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9579357877131569</v>
+        <v>0.9873620091244004</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.2373487486891304</v>
+        <v>-0.1637831951610234</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.687517382550881</v>
+        <v>2.731656714667746</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.790022301984887</v>
+        <v>-4.716456748456778</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8893033154178642</v>
+        <v>0.918729536829108</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.2373487486891304</v>
+        <v>-0.1637831951610234</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.663259411312088</v>
+        <v>2.707398743428953</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.756358756512605</v>
+        <v>-4.682793202984496</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9059001188266826</v>
+        <v>0.9353263402379264</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2036852032168485</v>
+        <v>-0.1301196496887415</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.686588923815363</v>
+        <v>2.730728255932227</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.696506137308882</v>
+        <v>-4.622940583780773</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9400135529403044</v>
+        <v>0.9694397743515479</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.2036852032168485</v>
+        <v>-0.1301196496887415</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.696761310247496</v>
+        <v>2.74090064236436</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.610262674282504</v>
+        <v>-4.536697120754395</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9694572087247157</v>
+        <v>0.9988834301359595</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.2036852032168485</v>
+        <v>-0.1301196496887415</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.691707580821356</v>
+        <v>2.73584691293822</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.655569493681484</v>
+        <v>-4.582003940153375</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9431102564096494</v>
+        <v>0.9725364778208929</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2444953662260793</v>
+        <v>-0.1709298126979723</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.658997258460343</v>
+        <v>2.703136590577207</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.684602598383785</v>
+        <v>-4.611037044855676</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9320488875618305</v>
+        <v>0.9614751089730742</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2444953662260793</v>
+        <v>-0.1709298126979723</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.659549131493445</v>
+        <v>2.703688463610309</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.591792116932925</v>
+        <v>-4.518226563404816</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8984457720335399</v>
+        <v>0.9278719934447837</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.15168488477522</v>
+        <v>-0.07811933124711296</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.644508112255326</v>
+        <v>2.68864744437219</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.636181586262353</v>
+        <v>-4.562616032734244</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8825634602263699</v>
+        <v>0.9119896816376134</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.1960743541046476</v>
+        <v>-0.1225088005765406</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.61974790658227</v>
+        <v>2.663887238699134</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.523510368026103</v>
+        <v>-4.449944814497994</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9227076560325929</v>
+        <v>0.9521338774438366</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.08340313586839743</v>
+        <v>-0.009837582340290418</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.682426346035743</v>
+        <v>2.726565678152607</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.41113336684343</v>
+        <v>-4.337567813315321</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9731497523363293</v>
+        <v>1.002575973747573</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.08340313586839743</v>
+        <v>-0.009837582340290418</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.68791764186641</v>
+        <v>2.732056973983275</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.438913764744782</v>
+        <v>-4.365348211216673</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9735347949443274</v>
+        <v>1.002961016355571</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1111835337697505</v>
+        <v>-0.03761798024164348</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.682746604894138</v>
+        <v>2.726885937011002</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.521915045770061</v>
+        <v>-4.448349492241952</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7786900025348691</v>
+        <v>0.8081162239461126</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1297544182969242</v>
+        <v>-0.05618886476881724</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.509959794178487</v>
+        <v>2.554099126295351</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.630529124213393</v>
+        <v>-4.556963570685284</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8553940318767421</v>
+        <v>0.8848202532879859</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1297544182969242</v>
+        <v>-0.05618886476881724</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.630109454897692</v>
+        <v>2.674248787014557</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.717127707194495</v>
+        <v>-4.643562153666386</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.835267624786624</v>
+        <v>0.8646938461978677</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1297544182969242</v>
+        <v>-0.05618886476881724</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.644622481000015</v>
+        <v>2.68876181311688</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.678744044636344</v>
+        <v>-4.605178491108235</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8480405311522532</v>
+        <v>0.8774667525634967</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.09137075573877307</v>
+        <v>-0.01780520221066606</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.665072119877275</v>
+        <v>2.709211451994139</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.501627714601178</v>
+        <v>-4.428062161073069</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9156160920116214</v>
+        <v>0.9450423134228652</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.09137075573877307</v>
+        <v>-0.01780520221066606</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.661801148722577</v>
+        <v>2.705940480839441</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.546719959434724</v>
+        <v>-4.473154405906615</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8982625858401163</v>
+        <v>0.9276888072513598</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1532667989081629</v>
+        <v>-0.07970124538005585</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.625346914582856</v>
+        <v>2.66948624669972</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.367344538195956</v>
+        <v>-4.293778984667847</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9637997296420378</v>
+        <v>0.9932259510532813</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.003509959262555817</v>
+        <v>0.07707551279066283</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.713199944791701</v>
+        <v>2.757339276908565</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.412358751716562</v>
+        <v>-4.338793198188453</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9266014995653853</v>
+        <v>0.9560277209766288</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.02683893605204879</v>
+        <v>0.04672661747605822</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.675798062934528</v>
+        <v>2.719937395051392</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.679363261988997</v>
+        <v>-4.605797708460888</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.825491257795357</v>
+        <v>0.8549174792066006</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2212019740949974</v>
+        <v>-0.1476364205668904</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.564871802447705</v>
+        <v>2.609011134564569</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.78056104342617</v>
+        <v>-4.706995489898061</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7842160671169893</v>
+        <v>0.8136422885282328</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2896107876403166</v>
+        <v>-0.2160452341122095</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.523030436217015</v>
+        <v>2.567169768333879</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.748085457255398</v>
+        <v>-4.674519903727289</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7948062631396149</v>
+        <v>0.8242324845508584</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2896107876403166</v>
+        <v>-0.2160452341122095</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.520630397771332</v>
+        <v>2.564769729888196</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.7290473295481</v>
+        <v>-4.655481776019991</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7989462334307786</v>
+        <v>0.8283724548420224</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3477943989715111</v>
+        <v>-0.2742288454434041</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.48224495018086</v>
+        <v>2.526384282297724</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.760173960698719</v>
+        <v>-4.68660840717061</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.964077449909212</v>
+        <v>0.9935036713204555</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3477943989715111</v>
+        <v>-0.2742288454434041</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.65982681911954</v>
+        <v>2.703966151236405</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.774040722032637</v>
+        <v>-4.700475168504528</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9593640743617784</v>
+        <v>0.9887902957730219</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.385652315705334</v>
+        <v>-0.312086762177227</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.63794539806538</v>
+        <v>2.682084730182244</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.794298020561595</v>
+        <v>-4.720732467033486</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.957269685347121</v>
+        <v>0.9866959067583647</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.385652315705334</v>
+        <v>-0.312086762177227</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.643953928462306</v>
+        <v>2.68809326057917</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.646555050326592</v>
+        <v>-4.572989496798483</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.095519521233144</v>
+        <v>1.124945742644388</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2178449584704509</v>
+        <v>-0.1442794049423439</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.823790990595258</v>
+        <v>2.867930322712122</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.748569732857813</v>
+        <v>-4.675004179329704</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.057507269752136</v>
+        <v>1.08693349116338</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2178449584704509</v>
+        <v>-0.1442794049423439</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.826584612126739</v>
+        <v>2.870723944243603</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.742417026805029</v>
+        <v>-4.66885147327692</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.060630700564908</v>
+        <v>1.090056921976152</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.2116922524176666</v>
+        <v>-0.1381266988895596</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.830938584150068</v>
+        <v>2.875077916266932</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.993044333682986</v>
+        <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.759226324955531</v>
+        <v>-4.685660771427422</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.088997379387027</v>
+        <v>1.082413679456062</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.2285015505681682</v>
+        <v>-0.1549359970400612</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.855943403342086</v>
+        <v>2.864072814116741</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.059379887479807</v>
+        <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.696928326179409</v>
+        <v>-4.6233627726513</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.180252132694297</v>
+        <v>1.173668432763332</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.2285015505681682</v>
+        <v>-0.1549359970400612</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.922278957138907</v>
+        <v>2.930408367913562</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992194</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.767960759869205</v>
+        <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.495138128514251</v>
+        <v>-4.421572574986142</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9695490841497578</v>
+        <v>0.9629653842187926</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.03048335839901384</v>
+        <v>0.04308219512909317</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.749670744829797</v>
+        <v>2.757800155604453</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.838250992191381</v>
+        <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.435247446871657</v>
+        <v>-4.361681893343548</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.06379558912897</v>
+        <v>1.057211889198005</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.02940732324357964</v>
+        <v>0.1029728767716866</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.855895386137528</v>
+        <v>2.864024796912184</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319549</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.852878728307424</v>
+        <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.532987991496632</v>
+        <v>-4.459422437968523</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.039327107395024</v>
+        <v>1.032743407464059</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.01351804511059945</v>
+        <v>0.08708359863870646</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.860989555373784</v>
+        <v>2.86911896614844</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489388</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.851414709132096</v>
+        <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.709325751619561</v>
+        <v>-4.635760198091452</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9673279841705242</v>
+        <v>0.960744284239559</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.1628197150123299</v>
+        <v>-0.08925416148422294</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.753722880124698</v>
+        <v>2.761852290899354</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397798</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.849906327172024</v>
+        <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.637779428842684</v>
+        <v>-4.564213875314575</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9944381313212034</v>
+        <v>0.9878544313902384</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.1628197150123299</v>
+        <v>-0.08925416148422294</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.752214498164627</v>
+        <v>2.760343908939282</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.836023391024965</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.849769194607461</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.593406297204115</v>
+        <v>-4.519840743676006</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.012050251412067</v>
+        <v>1.005466551481102</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.1184465833737613</v>
+        <v>-0.04488102984565434</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.778701244583204</v>
+        <v>2.78683065535786</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863226</v>
+        <v>3.821591150863225</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.849769194607461</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.585452326909343</v>
+        <v>-4.511886773381234</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.015231839529976</v>
+        <v>1.008648139599011</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.1184465833737613</v>
+        <v>-0.04488102984565434</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.778701244583204</v>
+        <v>2.78683065535786</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947585</v>
+        <v>3.833040181947584</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.856150951635265</v>
+        <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.537796596348287</v>
+        <v>-4.464231042820178</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.040675888782203</v>
+        <v>1.034092188851238</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.0707908528127057</v>
+        <v>0.002774700715401313</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.813676439947642</v>
+        <v>2.821805850722297</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326877</v>
+        <v>3.822707244326876</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.86104332500999</v>
+        <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.410112286553991</v>
+        <v>-4.336546733025882</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.096641986074646</v>
+        <v>1.090058286143681</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.05689345698159076</v>
+        <v>0.1304590105096978</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.895179399198945</v>
+        <v>2.9033088099736</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314553</v>
+        <v>3.828837911314552</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.847797997485862</v>
+        <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.470778876956381</v>
+        <v>-4.397213323428272</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.059130022389563</v>
+        <v>1.052546322458598</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.02480485973694291</v>
+        <v>0.0487606937911641</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.832915081643697</v>
+        <v>2.841044492418352</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690029</v>
+        <v>3.816866067690028</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.851895700096491</v>
+        <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.425940475347982</v>
+        <v>-4.352374921819873</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.081163085643551</v>
+        <v>1.074579385712586</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.02026142679207343</v>
+        <v>0.05330412673603357</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.839738844021247</v>
+        <v>2.847868254795903</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674313</v>
+        <v>3.817961388674311</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.856056639727569</v>
+        <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.52669911110498</v>
+        <v>-4.453133557576871</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.045020570971829</v>
+        <v>1.038436871040864</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.1090869955190789</v>
+        <v>-0.03552144199097185</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.790604442416122</v>
+        <v>2.798733853190777</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163222</v>
+        <v>3.82671377916322</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.861936242255406</v>
+        <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.48249627401908</v>
+        <v>-4.408930720490971</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.068581308334027</v>
+        <v>1.061997608403062</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.06488415843317841</v>
+        <v>0.008681395094928601</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.823005747195499</v>
+        <v>2.831135157970155</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022907</v>
+        <v>3.838228663022905</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.860346242724654</v>
+        <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.519475301682522</v>
+        <v>-4.445909748154413</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.052199697737897</v>
+        <v>1.045615997806932</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.02791025664184787</v>
+        <v>0.04565529688625913</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.843600088739545</v>
+        <v>2.8517294995142</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042141</v>
+        <v>3.863924114042139</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.911594007907693</v>
+        <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.539533380547363</v>
+        <v>-4.465967827019254</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.095424231375001</v>
+        <v>1.088840531444036</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.02791025664184787</v>
+        <v>0.04565529688625913</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.894847853922585</v>
+        <v>2.90297726469724</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078284</v>
+        <v>3.865367715078282</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.910034712501946</v>
+        <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.499602707369473</v>
+        <v>-4.426037153841364</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.10983720524041</v>
+        <v>1.103253505309445</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.01202041653604247</v>
+        <v>0.08558597006414947</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.917246962423572</v>
+        <v>2.925376373198227</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232401</v>
+        <v>3.864518876232399</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.904982940740216</v>
+        <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.448570614646945</v>
+        <v>-4.375005061118836</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.125198270567691</v>
+        <v>1.118614570636726</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.06305250925857042</v>
+        <v>0.1366180627866774</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.942814446295359</v>
+        <v>2.950943857070014</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162116</v>
+        <v>3.842576394162115</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.922170344832921</v>
+        <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.38334643351974</v>
+        <v>-4.309780879991631</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.168475347111278</v>
+        <v>1.161891647180313</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.128276690385776</v>
+        <v>0.2018422439138831</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.999136359064387</v>
+        <v>3.007265769839043</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.84009022063982</v>
+        <v>3.840090220639818</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.918131317132202</v>
+        <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.345919413448605</v>
+        <v>-4.272353859920496</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.179407127439012</v>
+        <v>1.172823427508047</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.1335282284149577</v>
+        <v>0.2070937819430647</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.998248254181176</v>
+        <v>3.006377664955832</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749925</v>
+        <v>3.845198842749923</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.919388109463442</v>
+        <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.366031069483314</v>
+        <v>-4.292465515955205</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.172619257356369</v>
+        <v>1.166035557425404</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.1445555734123769</v>
+        <v>0.2181211269404839</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.006121453510868</v>
+        <v>3.014250864285524</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393551</v>
+        <v>3.82869047939355</v>
       </c>
       <c r="C1991" t="n">
-        <v>3.079945880484653</v>
+        <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.312286255056109</v>
+        <v>-4.238720701528</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.354674954148462</v>
+        <v>1.348091254217497</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.1546188828528389</v>
+        <v>0.2281844363809459</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.172717210196356</v>
+        <v>3.180846620971012</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714889</v>
+        <v>3.813251854714887</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.20005878970247</v>
+        <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.325151999751778</v>
+        <v>-4.214929132921858</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.469641565488011</v>
+        <v>1.477720790877771</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.1417531381571694</v>
+        <v>0.2519760049870882</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.285110672596772</v>
+        <v>3.315234471352515</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756015</v>
+        <v>3.814259761756013</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.191766765716329</v>
+        <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.361906418313501</v>
+        <v>-4.25168355148358</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.446647774077181</v>
+        <v>1.454726999466941</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.1417531381571694</v>
+        <v>0.2519760049870882</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.276818648610631</v>
+        <v>3.306942447366374</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654189</v>
+        <v>3.803426852654187</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.189959961300108</v>
+        <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.357572115256453</v>
+        <v>-4.247349248426532</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.44657469088378</v>
+        <v>1.454653916273539</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.2934032414763733</v>
+        <v>0.4036261083062921</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.366001906185933</v>
+        <v>3.396125704941675</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.79629317771712</v>
+        <v>3.796293177717118</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.2075143670269</v>
+        <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.34867965386317</v>
+        <v>-4.238456787033249</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.467686081167885</v>
+        <v>1.475765306557644</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.2934032414763733</v>
+        <v>0.4036261083062921</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.383556311912724</v>
+        <v>3.413680110668467</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702628</v>
+        <v>3.794453975702626</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.199369414431484</v>
+        <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.517155770833047</v>
+        <v>-4.406932904003127</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.392150681784518</v>
+        <v>1.400229907174277</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.2654554057597925</v>
+        <v>0.3756782725897113</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.358642657887359</v>
+        <v>3.388766456643102</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795603100539971</v>
+        <v>3.795603100539969</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.269782075888327</v>
+        <v>3.233772154546119</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.819356241971464</v>
+        <v>-3.709133375141544</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.741683154785995</v>
+        <v>1.749762380175754</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.1951073463893818</v>
+        <v>0.3053302132193006</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.386846483721957</v>
+        <v>3.416970282477699</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784700379389901</v>
+        <v>3.784700379389899</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.260446098385232</v>
+        <v>3.224436177043023</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.796635138288311</v>
+        <v>-3.686412271458391</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.74143561875616</v>
+        <v>1.749514844145919</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.1951073463893818</v>
+        <v>0.3053302132193006</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.377510506218861</v>
+        <v>3.407634304974604</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783234730534939</v>
+        <v>3.783234730534937</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.419352224236401</v>
+        <v>3.383342302894192</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.936927737825504</v>
+        <v>-3.826704870995584</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.844224704792452</v>
+        <v>1.852303930182212</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.05481474685218918</v>
+        <v>0.165037613682108</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.452241072347715</v>
+        <v>3.482364871103457</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779962759401677</v>
+        <v>3.779962759401675</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.456430046730048</v>
+        <v>3.420420125387839</v>
       </c>
       <c r="D2000" t="n">
-        <v>-4.091708744603759</v>
+        <v>-3.981485877773839</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.819390124574797</v>
+        <v>1.827469349964556</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.02144707279771307</v>
+        <v>0.1316699396276318</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.469298290408676</v>
+        <v>3.499422089164418</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.579534779650182</v>
+        <v>3.831504253495862</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.368866080424836</v>
+        <v>3.484973467023984</v>
       </c>
       <c r="D2001" t="n">
-        <v>-4.091708744603759</v>
+        <v>-3.981485877773839</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.819390124574797</v>
+        <v>1.827469349964556</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.02144707279771307</v>
+        <v>0.1316699396276318</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.361929877411204</v>
+        <v>3.478037264010352</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240620.xlsx
+++ b/tame_output/ON/bt/strategyON_20240620.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>61.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>53.2%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>76.1%</t>
+          <t>74.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>30.0%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>-75.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.5%</t>
+          <t>-70.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-559.7%</t>
+          <t>-560.0%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-193.5%</t>
+          <t>-194.0%</t>
         </is>
       </c>
     </row>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-98.2%</t>
+          <t>-96.5%</t>
         </is>
       </c>
     </row>
@@ -46976,10 +46976,10 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.564213875314575</v>
+        <v>-4.558845033548594</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9878544313902384</v>
+        <v>0.9900019680966308</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.08925416148422294</v>
@@ -46999,10 +46999,10 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.519840743676006</v>
+        <v>-4.514471901910025</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.005466551481102</v>
+        <v>1.007614088187494</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.04488102984565434</v>
@@ -47022,10 +47022,10 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.511886773381234</v>
+        <v>-4.506517931615253</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.008648139599011</v>
+        <v>1.010795676305403</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.04488102984565434</v>
@@ -47045,10 +47045,10 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.464231042820178</v>
+        <v>-4.458862201054197</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.034092188851238</v>
+        <v>1.03623972555763</v>
       </c>
       <c r="F1978" t="n">
         <v>0.002774700715401313</v>
@@ -47068,10 +47068,10 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.336546733025882</v>
+        <v>-4.331177891259901</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.090058286143681</v>
+        <v>1.092205822850074</v>
       </c>
       <c r="F1979" t="n">
         <v>0.1304590105096978</v>
@@ -47091,10 +47091,10 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.397213323428272</v>
+        <v>-4.391844481662289</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.052546322458598</v>
+        <v>1.054693859164991</v>
       </c>
       <c r="F1980" t="n">
         <v>0.0487606937911641</v>
@@ -47114,10 +47114,10 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.352374921819873</v>
+        <v>-4.347006080053891</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.074579385712586</v>
+        <v>1.076726922418978</v>
       </c>
       <c r="F1981" t="n">
         <v>0.05330412673603357</v>
@@ -47137,10 +47137,10 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.453133557576871</v>
+        <v>-4.447764715810889</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.038436871040864</v>
+        <v>1.040584407747257</v>
       </c>
       <c r="F1982" t="n">
         <v>-0.03552144199097185</v>
@@ -47160,10 +47160,10 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.408930720490971</v>
+        <v>-4.403561878724989</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.061997608403062</v>
+        <v>1.064145145109455</v>
       </c>
       <c r="F1983" t="n">
         <v>0.008681395094928601</v>
@@ -47183,10 +47183,10 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.445909748154413</v>
+        <v>-4.440540906388431</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.045615997806932</v>
+        <v>1.047763534513325</v>
       </c>
       <c r="F1984" t="n">
         <v>0.04565529688625913</v>
@@ -47206,10 +47206,10 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.465967827019254</v>
+        <v>-4.460598985253272</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.088840531444036</v>
+        <v>1.090988068150428</v>
       </c>
       <c r="F1985" t="n">
         <v>0.04565529688625913</v>
@@ -47229,10 +47229,10 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.426037153841364</v>
+        <v>-4.420668312075382</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.103253505309445</v>
+        <v>1.105401042015838</v>
       </c>
       <c r="F1986" t="n">
         <v>0.08558597006414947</v>
@@ -47252,10 +47252,10 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.375005061118836</v>
+        <v>-4.369636219352854</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.118614570636726</v>
+        <v>1.120762107343119</v>
       </c>
       <c r="F1987" t="n">
         <v>0.1366180627866774</v>
@@ -47275,10 +47275,10 @@
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.309780879991631</v>
+        <v>-4.304412038225649</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.161891647180313</v>
+        <v>1.164039183886706</v>
       </c>
       <c r="F1988" t="n">
         <v>0.2018422439138831</v>
@@ -47298,10 +47298,10 @@
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.272353859920496</v>
+        <v>-4.266985018154514</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.172823427508047</v>
+        <v>1.17497096421444</v>
       </c>
       <c r="F1989" t="n">
         <v>0.2070937819430647</v>
@@ -47321,10 +47321,10 @@
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.292465515955205</v>
+        <v>-4.287096674189223</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.166035557425404</v>
+        <v>1.168183094131797</v>
       </c>
       <c r="F1990" t="n">
         <v>0.2181211269404839</v>
@@ -47344,10 +47344,10 @@
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.238720701528</v>
+        <v>-4.233351859762018</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.348091254217497</v>
+        <v>1.35023879092389</v>
       </c>
       <c r="F1991" t="n">
         <v>0.2281844363809459</v>
@@ -47367,10 +47367,10 @@
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.214929132921858</v>
+        <v>-4.209560291155876</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.477720790877771</v>
+        <v>1.479868327584164</v>
       </c>
       <c r="F1992" t="n">
         <v>0.2519760049870882</v>
@@ -47390,10 +47390,10 @@
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.25168355148358</v>
+        <v>-4.246314709717598</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.454726999466941</v>
+        <v>1.456874536173334</v>
       </c>
       <c r="F1993" t="n">
         <v>0.2519760049870882</v>
@@ -47413,10 +47413,10 @@
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.247349248426532</v>
+        <v>-4.24198040666055</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.454653916273539</v>
+        <v>1.456801452979932</v>
       </c>
       <c r="F1994" t="n">
         <v>0.4036261083062921</v>
@@ -47436,10 +47436,10 @@
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.238456787033249</v>
+        <v>-4.233087945267267</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.475765306557644</v>
+        <v>1.477912843264037</v>
       </c>
       <c r="F1995" t="n">
         <v>0.4036261083062921</v>
@@ -47459,10 +47459,10 @@
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.406932904003127</v>
+        <v>-4.401564062237145</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.400229907174277</v>
+        <v>1.40237744388067</v>
       </c>
       <c r="F1996" t="n">
         <v>0.3756782725897113</v>
@@ -47482,10 +47482,10 @@
         <v>3.233772154546119</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.709133375141544</v>
+        <v>-3.703764533375562</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.749762380175754</v>
+        <v>1.751909916882147</v>
       </c>
       <c r="F1997" t="n">
         <v>0.3053302132193006</v>
@@ -47505,10 +47505,10 @@
         <v>3.224436177043023</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.686412271458391</v>
+        <v>-3.681043429692409</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.749514844145919</v>
+        <v>1.751662380852312</v>
       </c>
       <c r="F1998" t="n">
         <v>0.3053302132193006</v>
@@ -47528,10 +47528,10 @@
         <v>3.383342302894192</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.826704870995584</v>
+        <v>-3.821336029229601</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.852303930182212</v>
+        <v>1.854451466888604</v>
       </c>
       <c r="F1999" t="n">
         <v>0.165037613682108</v>
@@ -47551,10 +47551,10 @@
         <v>3.420420125387839</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.981485877773839</v>
+        <v>-3.976117036007857</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.827469349964556</v>
+        <v>1.829616886670949</v>
       </c>
       <c r="F2000" t="n">
         <v>0.1316699396276318</v>
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.831504253495862</v>
+        <v>3.812547971857574</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.484973467023984</v>
+        <v>3.415891444408781</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.981485877773839</v>
+        <v>-3.984098667659006</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.827469349964556</v>
+        <v>1.821895553031431</v>
       </c>
       <c r="F2001" t="n">
         <v>0.1316699396276318</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.478037264010352</v>
+        <v>3.49489340818536</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240620.xlsx
+++ b/tame_output/ON/bt/strategyON_20240620.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.1%</t>
+          <t>-75.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.0%</t>
+          <t>109.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.3%</t>
+          <t>123.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.3%</t>
+          <t>-51.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.6%</t>
+          <t>-71.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.9%</t>
+          <t>454.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-560.0%</t>
+          <t>-567.4%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.0%</t>
+          <t>-40.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-33.5%</t>
+          <t>-47.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-194.0%</t>
+          <t>-197.0%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-20.8%</t>
+          <t>-22.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.2%</t>
+          <t>-32.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-13.8%</t>
+          <t>-15.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-97.6%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>-191.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-210.8%</t>
+          <t>-219.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>95.8%</t>
+          <t>96.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.7%</t>
+          <t>-28.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-17.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-96.5%</t>
+          <t>-101.4%</t>
         </is>
       </c>
     </row>
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.624990596265652</v>
+        <v>-9.69855614979376</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7155457676834036</v>
+        <v>-0.7449719890946467</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.020716896429177</v>
+        <v>-2.094282449957284</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.922376757279099</v>
+        <v>1.878237425162234</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.829248771595516</v>
+        <v>-9.902814325123623</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.791735840696707</v>
+        <v>-0.8211620621079496</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.148355841043166</v>
+        <v>-2.221921394571273</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.851306587629348</v>
+        <v>1.807167255512484</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.90358174785568</v>
+        <v>-9.977147301383788</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8169864767163366</v>
+        <v>-0.8464126981275792</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.293055364977838</v>
+        <v>-2.366620918505946</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.76896942775298</v>
+        <v>1.724830095636116</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.830111916188232</v>
+        <v>-9.903677469716339</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.772226842555936</v>
+        <v>-0.8016530639671786</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.21958553331039</v>
+        <v>-2.293151086838497</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.828423028246871</v>
+        <v>1.784283696130006</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.00523633357477</v>
+        <v>-10.07880188710288</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8277213887630364</v>
+        <v>-0.8571476101742794</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.394709950696934</v>
+        <v>-2.468275504225041</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.737903598562461</v>
+        <v>1.693764266445597</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.23968842758926</v>
+        <v>-10.31325398111737</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9287213912704284</v>
+        <v>-0.9581476126816715</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.394709950696934</v>
+        <v>-2.468275504225041</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.730684433660865</v>
+        <v>1.686545101544001</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.34406315861571</v>
+        <v>-10.41762871214382</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.9771434744549832</v>
+        <v>-1.006569695866226</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.499084681723379</v>
+        <v>-2.572650235251487</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.661387404271021</v>
+        <v>1.617248072154157</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.39684931421604</v>
+        <v>-10.47041486774414</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.9971421468565573</v>
+        <v>-1.0265683682678</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.594760168305776</v>
+        <v>-2.668325721833884</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.605097902160139</v>
+        <v>1.560958570043275</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.52288610758433</v>
+        <v>-10.59645166111243</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.044863135574758</v>
+        <v>-1.074289356986001</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.569508545496034</v>
+        <v>-2.643074099024141</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.6229426044751</v>
+        <v>1.578803272358235</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.47087059361551</v>
+        <v>-10.54443614714362</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.020066594300832</v>
+        <v>-1.049492815712076</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.569508545496034</v>
+        <v>-2.643074099024141</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.6269329401615</v>
+        <v>1.582793608044636</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.61254243533963</v>
+        <v>-10.68610798886774</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.078210557889222</v>
+        <v>-1.107636779300465</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.569508545496034</v>
+        <v>-2.643074099024141</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.625457713262759</v>
+        <v>1.581318381145894</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.5629515909148</v>
+        <v>-10.63651714444291</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.043320809954416</v>
+        <v>-1.072747031365659</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.5199177010712</v>
+        <v>-2.593483254599307</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.670265630082531</v>
+        <v>1.626126297965667</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.55014419791003</v>
+        <v>-10.62370975143813</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.05124898639919</v>
+        <v>-1.080675207810433</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.568773476080101</v>
+        <v>-2.642339029608209</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.627901031430508</v>
+        <v>1.583761699313643</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.32429904519061</v>
+        <v>-10.39786459871872</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.9513318522752159</v>
+        <v>-0.9807580736864598</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.526846800492938</v>
+        <v>-2.600412354021045</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.662636109819015</v>
+        <v>1.61849677770215</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.19972038885302</v>
+        <v>-10.27328594238113</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9003612451841208</v>
+        <v>-0.9297874665953638</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.526846800492938</v>
+        <v>-2.600412354021045</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.663775254375073</v>
+        <v>1.619635922258209</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.25261567689731</v>
+        <v>-10.32618123042542</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9188855862397274</v>
+        <v>-0.9483118076509713</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.521891454404491</v>
+        <v>-2.595457007932599</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.669382236190249</v>
+        <v>1.625242904073384</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.18048250160943</v>
+        <v>-10.25404805513754</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8842986118859386</v>
+        <v>-0.9137248332971817</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.521891454404491</v>
+        <v>-2.595457007932599</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.675115940428885</v>
+        <v>1.630976608312021</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.10911610899978</v>
+        <v>-10.18268166252789</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8654893172359444</v>
+        <v>-0.8949155386471883</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.450525061794843</v>
+        <v>-2.524090615322951</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.708198513600809</v>
+        <v>1.664059181483945</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.01565707501456</v>
+        <v>-10.08922262854266</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8379891849547625</v>
+        <v>-0.8674154063660064</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.450525061794843</v>
+        <v>-2.524090615322951</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.698315032287901</v>
+        <v>1.654175700171037</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.748415274146158</v>
+        <v>-9.821980827674267</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7329270251067772</v>
+        <v>-0.7623532465180207</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.450525061794843</v>
+        <v>-2.524090615322951</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.696480471788528</v>
+        <v>1.652341139671663</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.650508235469667</v>
+        <v>-9.724073788997776</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6940645246096415</v>
+        <v>-0.7234907460208855</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.382539311934287</v>
+        <v>-2.456104865462394</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.736971606731401</v>
+        <v>1.692832274614536</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.626554694493709</v>
+        <v>-9.700120248021818</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.683814602073765</v>
+        <v>-0.7132408234850085</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.358585770958329</v>
+        <v>-2.432151324486437</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.752012237462469</v>
+        <v>1.707872905345605</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.362494756170912</v>
+        <v>-9.436060309699021</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5914509429063983</v>
+        <v>-0.6208771643176418</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.094525832635533</v>
+        <v>-2.168091386163641</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.897187884294394</v>
+        <v>1.85304855217753</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.655415132666075</v>
+        <v>-8.728980686194184</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3114061271647643</v>
+        <v>-0.3408323485760079</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.094525832635533</v>
+        <v>-2.168091386163641</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.894400850634093</v>
+        <v>1.850261518517229</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.615230834299885</v>
+        <v>-8.688796387827994</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2949887839304468</v>
+        <v>-0.3244150053416903</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.054341534269343</v>
+        <v>-2.12790708779745</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.918855053541649</v>
+        <v>1.874715721424785</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.451830963360521</v>
+        <v>-8.52539651688863</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2302620143339444</v>
+        <v>-0.259688235745188</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.89094166332998</v>
+        <v>-1.964507216858087</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.016261797326024</v>
+        <v>1.972122465209159</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.218349741130922</v>
+        <v>-8.291915294659031</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1289450966042525</v>
+        <v>-0.158371318015496</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.657460441100381</v>
+        <v>-1.731025994628489</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.164274959501635</v>
+        <v>2.120135627384771</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.068683350123408</v>
+        <v>-8.142248903651517</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.07197075051420576</v>
+        <v>-0.1013969719254493</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.564556949857846</v>
+        <v>-1.638122503385953</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.217124843934198</v>
+        <v>2.172985511817333</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.936407876492521</v>
+        <v>-8.009973430020629</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.02369307431482426</v>
+        <v>-0.05311929572606733</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.432281476226959</v>
+        <v>-1.505847029755066</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.291857614859757</v>
+        <v>2.247718282742892</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.745808201819369</v>
+        <v>-7.819373755347477</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.05536185624207368</v>
+        <v>0.02593563483083017</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.241681801553806</v>
+        <v>-1.315247355081913</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.409032480351285</v>
+        <v>2.364893148234421</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.496808403135788</v>
+        <v>-7.570373956663896</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1678681169391649</v>
+        <v>0.1384418955279214</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.241681801553806</v>
+        <v>-1.315247355081913</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.421938821574944</v>
+        <v>2.377799489458079</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.602398392908892</v>
+        <v>-7.675963946437</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.002343808569295724</v>
+        <v>-0.03177002998053879</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.34727179132691</v>
+        <v>-1.420837344855018</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.230608898111862</v>
+        <v>2.186469565994998</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.621133295027489</v>
+        <v>-7.694698848555597</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.03870657246035192</v>
+        <v>0.009280351049108404</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.352867800987042</v>
+        <v>-1.426433354515149</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.27579563419287</v>
+        <v>2.231656302076006</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.47319325361989</v>
+        <v>-7.546758807147998</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.02199633366477594</v>
+        <v>-0.05142255507601945</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.332546885078484</v>
+        <v>-1.406112438606591</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.168109261049837</v>
+        <v>2.123969928932973</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.420223731365901</v>
+        <v>-7.493789284894009</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.009522511016658797</v>
+        <v>-0.03894873242790187</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.279577362824495</v>
+        <v>-1.353142916352602</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.191176988148752</v>
+        <v>2.147037656031888</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.376675324595211</v>
+        <v>-7.450240878123319</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.0009362395965242243</v>
+        <v>-0.02848998181471885</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.279577362824495</v>
+        <v>-1.353142916352602</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.184216376053659</v>
+        <v>2.140077043936795</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.134526931141353</v>
+        <v>-7.208092484669461</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1122579513592106</v>
+        <v>0.0828317299479675</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.279577362824495</v>
+        <v>-1.353142916352602</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.198678730434802</v>
+        <v>2.154539398317938</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.026267794018831</v>
+        <v>-7.099833347546939</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1500937266674143</v>
+        <v>0.1206675052561712</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.279577362824495</v>
+        <v>-1.353142916352602</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.193210850893997</v>
+        <v>2.149071518777133</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.9029766592017</v>
+        <v>-6.976542212729808</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1969082746048434</v>
+        <v>0.1674820531936003</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.156286228007365</v>
+        <v>-1.229851781535472</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.264683625794852</v>
+        <v>2.220544293677988</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.881827460298257</v>
+        <v>-6.955393013826365</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2130689324035462</v>
+        <v>0.1836427109923027</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.135137029103921</v>
+        <v>-1.208702582632029</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.285074123374244</v>
+        <v>2.240934791257379</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.638062018314812</v>
+        <v>-6.711627571842921</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3063558175439742</v>
+        <v>0.2769295961327312</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.135137029103921</v>
+        <v>-1.208702582632029</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.280854831721294</v>
+        <v>2.23671549960443</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.536299198037518</v>
+        <v>-6.609864751565626</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3491852595749085</v>
+        <v>0.319759038163665</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.121917960711493</v>
+        <v>-1.1954835142396</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.290910586676767</v>
+        <v>2.246771254559903</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.286448804088443</v>
+        <v>-6.360014357616551</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4418674921382402</v>
+        <v>0.4124412707269971</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.121917960711493</v>
+        <v>-1.1954835142396</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.28365266166047</v>
+        <v>2.239513329543605</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.11055671162101</v>
+        <v>-6.184122265149119</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5158234526458623</v>
+        <v>0.4863972312346188</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.121917960711493</v>
+        <v>-1.1954835142396</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.287251785181118</v>
+        <v>2.243112453064254</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.939110248598547</v>
+        <v>-6.012675802126656</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5977295439094013</v>
+        <v>0.5683033224981577</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.9504714976890295</v>
+        <v>-1.024037051217137</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.40344716904915</v>
+        <v>2.359307836932286</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.864820682860207</v>
+        <v>-5.938386236388316</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6264658478210339</v>
+        <v>0.5970396264097904</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.8761819319506903</v>
+        <v>-0.9497474854787973</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.447041386108451</v>
+        <v>2.402902053991586</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.801184940626273</v>
+        <v>-5.874750494154382</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6566149457689252</v>
+        <v>0.6271887243576817</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8125461897167557</v>
+        <v>-0.8861117432448627</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.489917632503128</v>
+        <v>2.445778300386264</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.689758181300353</v>
+        <v>-5.763323734828462</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6823799082830888</v>
+        <v>0.6529536868718453</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8125461897167557</v>
+        <v>-0.8861117432448627</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.471111891286924</v>
+        <v>2.42697255917006</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.449327684495493</v>
+        <v>-5.522893238023602</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7802951836299101</v>
+        <v>0.7508689622186666</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.5721156929118955</v>
+        <v>-0.6456812464400025</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.617113265994718</v>
+        <v>2.572973933877853</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.377085116324298</v>
+        <v>-5.450650669852407</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8131215247332082</v>
+        <v>0.7836953033219647</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.5721156929118955</v>
+        <v>-0.6456812464400025</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.621042579829538</v>
+        <v>2.576903247712674</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.32408679404291</v>
+        <v>-5.397652347571019</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8349994375631034</v>
+        <v>0.8055732161518598</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5167794339099566</v>
+        <v>-0.5903449874380636</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.654922919148041</v>
+        <v>2.610783587031177</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.215281908563183</v>
+        <v>-5.288847462091292</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8755194629749878</v>
+        <v>0.8460932415637443</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5167794339099566</v>
+        <v>-0.5903449874380636</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.651920990368035</v>
+        <v>2.607781658251171</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.995261110526172</v>
+        <v>-5.068826664054281</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9651068192004062</v>
+        <v>0.9356805977891627</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.3755595888419764</v>
+        <v>-0.4491251423700834</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.738231934419437</v>
+        <v>2.694092602302573</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.862393421462895</v>
+        <v>-4.935958974991004</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.03414807762754</v>
+        <v>1.004721856216297</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.3755595888419764</v>
+        <v>-0.4491251423700834</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.75412611722126</v>
+        <v>2.709986785104396</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.742220338098396</v>
+        <v>-4.815785891626505</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.083363155413642</v>
+        <v>1.053936934002398</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.2553865054774774</v>
+        <v>-0.3289520590055844</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.827375811680261</v>
+        <v>2.783236479563397</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.597548192998659</v>
+        <v>-4.671113746526768</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.151320116014977</v>
+        <v>1.121893894603733</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.11071436037774</v>
+        <v>-0.184279913905847</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.924267201301544</v>
+        <v>2.88012786918468</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.657423020356351</v>
+        <v>-4.73098857388446</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.113407676473326</v>
+        <v>1.083981455062082</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.1705891877354321</v>
+        <v>-0.2441547412635391</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.874379796288354</v>
+        <v>2.83024046417149</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.570623522577343</v>
+        <v>-4.644189076105452</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.170527968907495</v>
+        <v>1.141101747496251</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.1705891877354321</v>
+        <v>-0.2441547412635391</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.89678028961092</v>
+        <v>2.852640957494056</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.573093229039149</v>
+        <v>-4.646658782567258</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.169612487696185</v>
+        <v>1.140186266284941</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.1730588941972383</v>
+        <v>-0.2466244477253453</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.895370867107249</v>
+        <v>2.851231534990385</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.641463415363159</v>
+        <v>-4.715028968891268</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.153271335641283</v>
+        <v>1.123845114230039</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.1637831951610234</v>
+        <v>-0.2373487486891304</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.91194320900368</v>
+        <v>2.867803876886815</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.750001596279293</v>
+        <v>-4.823567149807402</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.10029277190672</v>
+        <v>1.070866550495477</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.1637831951610234</v>
+        <v>-0.2373487486891304</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.902379917635571</v>
+        <v>2.858240585518707</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.780994755607998</v>
+        <v>-4.854560309136107</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9126050732156252</v>
+        <v>0.8831788518043815</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.1637831951610234</v>
+        <v>-0.2373487486891304</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.727089482675958</v>
+        <v>2.682950150559094</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.605520495815529</v>
+        <v>-4.679086049343638</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9873620091244004</v>
+        <v>0.9579357877131569</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.1637831951610234</v>
+        <v>-0.2373487486891304</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.731656714667746</v>
+        <v>2.687517382550881</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.716456748456778</v>
+        <v>-4.790022301984887</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.918729536829108</v>
+        <v>0.8893033154178642</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.1637831951610234</v>
+        <v>-0.2373487486891304</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.707398743428953</v>
+        <v>2.663259411312088</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.682793202984496</v>
+        <v>-4.756358756512605</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9353263402379264</v>
+        <v>0.9059001188266826</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.1301196496887415</v>
+        <v>-0.2036852032168485</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.730728255932227</v>
+        <v>2.686588923815363</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.622940583780773</v>
+        <v>-4.696506137308882</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9694397743515479</v>
+        <v>0.9400135529403044</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.1301196496887415</v>
+        <v>-0.2036852032168485</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.74090064236436</v>
+        <v>2.696761310247496</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.536697120754395</v>
+        <v>-4.610262674282504</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9988834301359595</v>
+        <v>0.9694572087247157</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.1301196496887415</v>
+        <v>-0.2036852032168485</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.73584691293822</v>
+        <v>2.691707580821356</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.582003940153375</v>
+        <v>-4.655569493681484</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9725364778208929</v>
+        <v>0.9431102564096494</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.1709298126979723</v>
+        <v>-0.2444953662260793</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.703136590577207</v>
+        <v>2.658997258460343</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.611037044855676</v>
+        <v>-4.684602598383785</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9614751089730742</v>
+        <v>0.9320488875618305</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.1709298126979723</v>
+        <v>-0.2444953662260793</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.703688463610309</v>
+        <v>2.659549131493445</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.518226563404816</v>
+        <v>-4.591792116932925</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9278719934447837</v>
+        <v>0.8984457720335399</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.07811933124711296</v>
+        <v>-0.15168488477522</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.68864744437219</v>
+        <v>2.644508112255326</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.562616032734244</v>
+        <v>-4.636181586262353</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9119896816376134</v>
+        <v>0.8825634602263699</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.1225088005765406</v>
+        <v>-0.1960743541046476</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.663887238699134</v>
+        <v>2.61974790658227</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.449944814497994</v>
+        <v>-4.523510368026103</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9521338774438366</v>
+        <v>0.9227076560325929</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.009837582340290418</v>
+        <v>-0.08340313586839743</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.726565678152607</v>
+        <v>2.682426346035743</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.337567813315321</v>
+        <v>-4.41113336684343</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.002575973747573</v>
+        <v>0.9731497523363293</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.009837582340290418</v>
+        <v>-0.08340313586839743</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.732056973983275</v>
+        <v>2.68791764186641</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.365348211216673</v>
+        <v>-4.438913764744782</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.002961016355571</v>
+        <v>0.9735347949443274</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.03761798024164348</v>
+        <v>-0.1111835337697505</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.726885937011002</v>
+        <v>2.682746604894138</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.448349492241952</v>
+        <v>-4.521915045770061</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8081162239461126</v>
+        <v>0.7786900025348691</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.05618886476881724</v>
+        <v>-0.1297544182969242</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.554099126295351</v>
+        <v>2.509959794178487</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.556963570685284</v>
+        <v>-4.630529124213393</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8848202532879859</v>
+        <v>0.8553940318767421</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.05618886476881724</v>
+        <v>-0.1297544182969242</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.674248787014557</v>
+        <v>2.630109454897692</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.643562153666386</v>
+        <v>-4.717127707194495</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8646938461978677</v>
+        <v>0.835267624786624</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.05618886476881724</v>
+        <v>-0.1297544182969242</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.68876181311688</v>
+        <v>2.644622481000015</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.605178491108235</v>
+        <v>-4.678744044636344</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8774667525634967</v>
+        <v>0.8480405311522532</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.01780520221066606</v>
+        <v>-0.09137075573877307</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.709211451994139</v>
+        <v>2.665072119877275</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.428062161073069</v>
+        <v>-4.501627714601178</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9450423134228652</v>
+        <v>0.9156160920116214</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.01780520221066606</v>
+        <v>-0.09137075573877307</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.705940480839441</v>
+        <v>2.661801148722577</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.473154405906615</v>
+        <v>-4.546719959434724</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9276888072513598</v>
+        <v>0.8982625858401163</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.07970124538005585</v>
+        <v>-0.1532667989081629</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.66948624669972</v>
+        <v>2.625346914582856</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.293778984667847</v>
+        <v>-4.367344538195956</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9932259510532813</v>
+        <v>0.9637997296420378</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.07707551279066283</v>
+        <v>0.003509959262555817</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.757339276908565</v>
+        <v>2.713199944791701</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.338793198188453</v>
+        <v>-4.412358751716562</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9560277209766288</v>
+        <v>0.9266014995653853</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.04672661747605822</v>
+        <v>-0.02683893605204879</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.719937395051392</v>
+        <v>2.675798062934528</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.605797708460888</v>
+        <v>-4.679363261988997</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8549174792066006</v>
+        <v>0.825491257795357</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.1476364205668904</v>
+        <v>-0.2212019740949974</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.609011134564569</v>
+        <v>2.564871802447705</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.706995489898061</v>
+        <v>-4.78056104342617</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8136422885282328</v>
+        <v>0.7842160671169893</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2160452341122095</v>
+        <v>-0.2896107876403166</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.567169768333879</v>
+        <v>2.523030436217015</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.674519903727289</v>
+        <v>-4.748085457255398</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8242324845508584</v>
+        <v>0.7948062631396149</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2160452341122095</v>
+        <v>-0.2896107876403166</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.564769729888196</v>
+        <v>2.520630397771332</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.655481776019991</v>
+        <v>-4.7290473295481</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8283724548420224</v>
+        <v>0.7989462334307786</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.2742288454434041</v>
+        <v>-0.3477943989715111</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.526384282297724</v>
+        <v>2.48224495018086</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.68660840717061</v>
+        <v>-4.760173960698719</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9935036713204555</v>
+        <v>0.964077449909212</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.2742288454434041</v>
+        <v>-0.3477943989715111</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.703966151236405</v>
+        <v>2.65982681911954</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.700475168504528</v>
+        <v>-4.774040722032637</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9887902957730219</v>
+        <v>0.9593640743617784</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.312086762177227</v>
+        <v>-0.385652315705334</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.682084730182244</v>
+        <v>2.63794539806538</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.720732467033486</v>
+        <v>-4.794298020561595</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9866959067583647</v>
+        <v>0.957269685347121</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.312086762177227</v>
+        <v>-0.385652315705334</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.68809326057917</v>
+        <v>2.643953928462306</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.572989496798483</v>
+        <v>-4.646555050326592</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.124945742644388</v>
+        <v>1.095519521233144</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.1442794049423439</v>
+        <v>-0.2178449584704509</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.867930322712122</v>
+        <v>2.823790990595258</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.675004179329704</v>
+        <v>-4.748569732857813</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.08693349116338</v>
+        <v>1.057507269752136</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.1442794049423439</v>
+        <v>-0.2178449584704509</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.870723944243603</v>
+        <v>2.826584612126739</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.66885147327692</v>
+        <v>-4.742417026805029</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.090056921976152</v>
+        <v>1.060630700564908</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.1381266988895596</v>
+        <v>-0.2116922524176666</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.875077916266932</v>
+        <v>2.830938584150068</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.685660771427422</v>
+        <v>-4.759226324955531</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.082413679456062</v>
+        <v>1.052987458044818</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.1549359970400612</v>
+        <v>-0.2285015505681682</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.864072814116741</v>
+        <v>2.819933481999877</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.6233627726513</v>
+        <v>-4.696928326179409</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.173668432763332</v>
+        <v>1.144242211352088</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.1549359970400612</v>
+        <v>-0.2285015505681682</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.930408367913562</v>
+        <v>2.886269035796698</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.421572574986142</v>
+        <v>-4.495138128514251</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9629653842187926</v>
+        <v>0.9335391628075491</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.04308219512909317</v>
+        <v>-0.03048335839901384</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.757800155604453</v>
+        <v>2.713660823487589</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.361681893343548</v>
+        <v>-4.435247446871657</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.057211889198005</v>
+        <v>1.027785667786762</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.1029728767716866</v>
+        <v>0.02940732324357964</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.864024796912184</v>
+        <v>2.81988546479532</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.459422437968523</v>
+        <v>-4.532987991496632</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.032743407464059</v>
+        <v>1.003317186052815</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.08708359863870646</v>
+        <v>0.01351804511059945</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.86911896614844</v>
+        <v>2.824979634031576</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.635760198091452</v>
+        <v>-4.709325751619561</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.960744284239559</v>
+        <v>0.9313180628283155</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.08925416148422294</v>
+        <v>-0.1628197150123299</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.761852290899354</v>
+        <v>2.71771295878249</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.558845033548594</v>
+        <v>-4.632903705187634</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9900019680966308</v>
+        <v>0.9603784994410147</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.08925416148422294</v>
+        <v>-0.1628197150123299</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.760343908939282</v>
+        <v>2.716204576822418</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.514471901910025</v>
+        <v>-4.588530573549066</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.007614088187494</v>
+        <v>0.9779906195318784</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.04488102984565434</v>
+        <v>-0.1184465833737613</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.78683065535786</v>
+        <v>2.742691323240996</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863225</v>
+        <v>3.821591150863226</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.506517931615253</v>
+        <v>-4.580576603254293</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.010795676305403</v>
+        <v>0.9811722076497873</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.04488102984565434</v>
+        <v>-0.1184465833737613</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.78683065535786</v>
+        <v>2.742691323240996</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947584</v>
+        <v>3.833040181947585</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.458862201054197</v>
+        <v>-4.532920872693238</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.03623972555763</v>
+        <v>1.006616256902014</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.002774700715401313</v>
+        <v>-0.0707908528127057</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.821805850722297</v>
+        <v>2.777666518605433</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326876</v>
+        <v>3.822707244326877</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.331177891259901</v>
+        <v>-4.405236562898941</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.092205822850074</v>
+        <v>1.062582354194458</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.1304590105096978</v>
+        <v>0.05689345698159076</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.9033088099736</v>
+        <v>2.859169477856736</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314552</v>
+        <v>3.828837911314553</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.391844481662289</v>
+        <v>-4.46590315330133</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.054693859164991</v>
+        <v>1.025070390509374</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.0487606937911641</v>
+        <v>-0.02480485973694291</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.841044492418352</v>
+        <v>2.796905160301488</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690028</v>
+        <v>3.816866067690029</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.347006080053891</v>
+        <v>-4.421064751692931</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.076726922418978</v>
+        <v>1.047103453763362</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.05330412673603357</v>
+        <v>-0.02026142679207343</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.847868254795903</v>
+        <v>2.803728922679039</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674311</v>
+        <v>3.817961388674313</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.447764715810889</v>
+        <v>-4.521823387449929</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.040584407747257</v>
+        <v>1.010960939091641</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.03552144199097185</v>
+        <v>-0.1090869955190789</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.798733853190777</v>
+        <v>2.754594521073913</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.82671377916322</v>
+        <v>3.826713779163222</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.403561878724989</v>
+        <v>-4.477620550364029</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.064145145109455</v>
+        <v>1.034521676453839</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.008681395094928601</v>
+        <v>-0.06488415843317841</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.831135157970155</v>
+        <v>2.78699582585329</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022905</v>
+        <v>3.838228663022907</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.440540906388431</v>
+        <v>-4.514599578027472</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.047763534513325</v>
+        <v>1.018140065857709</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.04565529688625913</v>
+        <v>-0.02791025664184787</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.8517294995142</v>
+        <v>2.807590167397336</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042139</v>
+        <v>3.863924114042141</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.460598985253272</v>
+        <v>-4.534657656892312</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.090988068150428</v>
+        <v>1.061364599494812</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.04565529688625913</v>
+        <v>-0.02791025664184787</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.90297726469724</v>
+        <v>2.858837932580376</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078282</v>
+        <v>3.865367715078284</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.420668312075382</v>
+        <v>-4.494726983714422</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.105401042015838</v>
+        <v>1.075777573360222</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.08558597006414947</v>
+        <v>0.01202041653604247</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.925376373198227</v>
+        <v>2.881237041081363</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232399</v>
+        <v>3.864518876232401</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.369636219352854</v>
+        <v>-4.443694890991894</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.120762107343119</v>
+        <v>1.091138638687503</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.1366180627866774</v>
+        <v>0.06305250925857042</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.950943857070014</v>
+        <v>2.90680452495315</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162115</v>
+        <v>3.842576394162116</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.304412038225649</v>
+        <v>-4.378470709864689</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.164039183886706</v>
+        <v>1.13441571523109</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.2018422439138831</v>
+        <v>0.128276690385776</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.007265769839043</v>
+        <v>2.963126437722178</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639818</v>
+        <v>3.84009022063982</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.266985018154514</v>
+        <v>-4.341043689793555</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.17497096421444</v>
+        <v>1.145347495558824</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.2070937819430647</v>
+        <v>0.1335282284149577</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.006377664955832</v>
+        <v>2.962238332838968</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749923</v>
+        <v>3.845198842749925</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.287096674189223</v>
+        <v>-4.361155345828263</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.168183094131797</v>
+        <v>1.138559625476181</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.2181211269404839</v>
+        <v>0.1445555734123769</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.014250864285524</v>
+        <v>2.97011153216866</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.82869047939355</v>
+        <v>3.828690479393551</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.233351859762018</v>
+        <v>-4.307410531401058</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.35023879092389</v>
+        <v>1.320615322268273</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.2281844363809459</v>
+        <v>0.1546188828528389</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.180846620971012</v>
+        <v>3.136707288854148</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714887</v>
+        <v>3.813251854714889</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.209560291155876</v>
+        <v>-4.283618962794916</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.479868327584164</v>
+        <v>1.450244858928547</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.2519760049870882</v>
+        <v>0.1784104514589812</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.315234471352515</v>
+        <v>3.27109513923565</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756013</v>
+        <v>3.814259761756015</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.246314709717598</v>
+        <v>-4.320373381356639</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.456874536173334</v>
+        <v>1.427251067517717</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.2519760049870882</v>
+        <v>0.1784104514589812</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.306942447366374</v>
+        <v>3.262803115249509</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654187</v>
+        <v>3.803426852654189</v>
       </c>
       <c r="C1994" t="n">
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.24198040666055</v>
+        <v>-4.316039078299591</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.456801452979932</v>
+        <v>1.427177984324316</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.4036261083062921</v>
+        <v>0.3300605547781851</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.396125704941675</v>
+        <v>3.351986372824811</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717118</v>
+        <v>3.79629317771712</v>
       </c>
       <c r="C1995" t="n">
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.233087945267267</v>
+        <v>-4.307146616906308</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.477912843264037</v>
+        <v>1.448289374608421</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.4036261083062921</v>
+        <v>0.3300605547781851</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.413680110668467</v>
+        <v>3.369540778551603</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702626</v>
+        <v>3.794453975702628</v>
       </c>
       <c r="C1996" t="n">
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.401564062237145</v>
+        <v>-4.475622733876185</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.40237744388067</v>
+        <v>1.372753975225054</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.3756782725897113</v>
+        <v>0.3021127190616043</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.388766456643102</v>
+        <v>3.344627124526238</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795603100539969</v>
+        <v>3.795603100539971</v>
       </c>
       <c r="C1997" t="n">
         <v>3.233772154546119</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.703764533375562</v>
+        <v>-3.777823205014602</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.751909916882147</v>
+        <v>1.722286448226531</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.3053302132193006</v>
+        <v>0.2317646596911936</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.416970282477699</v>
+        <v>3.372830950360835</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784700379389899</v>
+        <v>3.784700379389901</v>
       </c>
       <c r="C1998" t="n">
         <v>3.224436177043023</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.681043429692409</v>
+        <v>-3.755102101331449</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.751662380852312</v>
+        <v>1.722038912196696</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.3053302132193006</v>
+        <v>0.2317646596911936</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.407634304974604</v>
+        <v>3.363494972857739</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783234730534937</v>
+        <v>3.783234730534939</v>
       </c>
       <c r="C1999" t="n">
         <v>3.383342302894192</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.821336029229601</v>
+        <v>-3.895394700868642</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.854451466888604</v>
+        <v>1.824827998232988</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.165037613682108</v>
+        <v>0.09147206015400094</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.482364871103457</v>
+        <v>3.438225538986593</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779962759401675</v>
+        <v>3.779962759401677</v>
       </c>
       <c r="C2000" t="n">
         <v>3.420420125387839</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.976117036007857</v>
+        <v>-4.050175707646897</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.829616886670949</v>
+        <v>1.799993418015333</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.1316699396276318</v>
+        <v>0.05810438609952484</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.499422089164418</v>
+        <v>3.455282757047554</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.812547971857574</v>
+        <v>3.812547971857576</v>
       </c>
       <c r="C2001" t="n">
         <v>3.415891444408781</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.984098667659006</v>
+        <v>-4.058174320791693</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.821895553031431</v>
+        <v>1.792265291778356</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.1316699396276318</v>
+        <v>0.0501057729547289</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.49489340818536</v>
+        <v>3.445954908181618</v>
       </c>
     </row>
   </sheetData>
